--- a/rapporten/prijsrapport-2026-04-12.xlsx
+++ b/rapporten/prijsrapport-2026-04-12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="124">
   <si>
     <t>Product</t>
   </si>
@@ -37,289 +37,352 @@
     <t>Fulfilment</t>
   </si>
   <si>
+    <t>Creation Lamis Ruler Giftset</t>
+  </si>
+  <si>
     <t>6291012002678</t>
   </si>
   <si>
-    <t>1848492</t>
+    <t>De Koopjeshoek</t>
   </si>
   <si>
     <t>FBR</t>
   </si>
   <si>
-    <t>8715658350514</t>
-  </si>
-  <si>
-    <t>1762224</t>
-  </si>
-  <si>
-    <t>Omerta Express Sensualite Frivole 100ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8715658380238</t>
-  </si>
-  <si>
-    <t>8721055493105</t>
-  </si>
-  <si>
-    <t>7640158816851</t>
+    <t>Hello Kitty You're Cute Eau de Parfum voor Kinderen 50ml</t>
+  </si>
+  <si>
+    <t>8721055493303</t>
+  </si>
+  <si>
+    <t>Koopjesfun.nl</t>
+  </si>
+  <si>
+    <t>Hello Kitty Giftset 3 x 15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158817032</t>
+  </si>
+  <si>
+    <t>Omerta - Ma Merveilleuse - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658997443</t>
+  </si>
+  <si>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
+    <t>5414666014427</t>
+  </si>
+  <si>
+    <t>Juwelium</t>
+  </si>
+  <si>
+    <t>Real Time - Black Warrior - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658009566</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493860</t>
+  </si>
+  <si>
+    <t>Minimarkt W&amp;M</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494225</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494263</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816691</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816677</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816653</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494270</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494232</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Sparkle- Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493891</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816714</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816615</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493211</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816790</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816639</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493884</t>
+  </si>
+  <si>
+    <t>Hello Kitty - Giftset - Kisses - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
   </si>
   <si>
     <t>8721055493440</t>
   </si>
   <si>
-    <t>Omerta - Ma Merveilleuse - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658997443</t>
+    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816837</t>
+  </si>
+  <si>
+    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816813</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Smile - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493853</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Shine - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493877</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493198</t>
+  </si>
+  <si>
+    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493228</t>
+  </si>
+  <si>
+    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658370505</t>
+  </si>
+  <si>
+    <t>Bliksma Retail B.V.</t>
+  </si>
+  <si>
+    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
+  </si>
+  <si>
+    <t>8715658370062</t>
+  </si>
+  <si>
+    <t>Bubble Bliss Unicorn Giftbook Parfum Dreamy Glitterwings EDP voor meisjes 50ml</t>
+  </si>
+  <si>
+    <t>8721055492245</t>
+  </si>
+  <si>
+    <t>Dorall Twilight Wilderness - Herenparfum eau de toilette - 100 ml</t>
+  </si>
+  <si>
+    <t>6291012874381</t>
+  </si>
+  <si>
+    <t>Creation Lamis Golden Wave for Men Giftset</t>
+  </si>
+  <si>
+    <t>6291012002661</t>
+  </si>
+  <si>
+    <t>Real Time Hunted For Men - eau de toilette voor heren - 100ML</t>
   </si>
   <si>
     <t>8715658350521</t>
   </si>
   <si>
-    <t>8721055495826</t>
-  </si>
-  <si>
-    <t>5414666014427</t>
-  </si>
-  <si>
-    <t>1692530</t>
-  </si>
-  <si>
-    <t>8715658998952</t>
-  </si>
-  <si>
-    <t>Omerta - Royal X - Eau de toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370260</t>
-  </si>
-  <si>
-    <t>6291012874428</t>
-  </si>
-  <si>
-    <t>8715658360865</t>
-  </si>
-  <si>
-    <t>Bubble Bliss Unicorn Giftbook Parfum Dreamy Glitterwings EDP voor meisjes 50ml</t>
-  </si>
-  <si>
-    <t>8721055492245</t>
-  </si>
-  <si>
-    <t>NG Axure Sport Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>8719214758325</t>
-  </si>
-  <si>
-    <t>8718421831913</t>
-  </si>
-  <si>
-    <t>6291012002692</t>
-  </si>
-  <si>
-    <t>8715658380412</t>
-  </si>
-  <si>
-    <t>6291012905399</t>
-  </si>
-  <si>
-    <t>8715658340287</t>
-  </si>
-  <si>
-    <t>8715658370208</t>
-  </si>
-  <si>
-    <t>Next Generation Touch Desire Eau de Parfum 80ml</t>
-  </si>
-  <si>
-    <t>8719214752699</t>
-  </si>
-  <si>
-    <t>8715658350705</t>
-  </si>
-  <si>
-    <t>8721055493068</t>
-  </si>
-  <si>
-    <t>5414666010511</t>
-  </si>
-  <si>
-    <t>8721055493860</t>
-  </si>
-  <si>
-    <t>946246</t>
-  </si>
-  <si>
-    <t>8721055494225</t>
-  </si>
-  <si>
-    <t>8721055494263</t>
-  </si>
-  <si>
-    <t>7640158816691</t>
-  </si>
-  <si>
-    <t>7640158816677</t>
-  </si>
-  <si>
-    <t>7640158816653</t>
-  </si>
-  <si>
-    <t>8721055494270</t>
-  </si>
-  <si>
-    <t>8721055494232</t>
-  </si>
-  <si>
-    <t>8721055493891</t>
-  </si>
-  <si>
-    <t>7640158816714</t>
-  </si>
-  <si>
-    <t>7640158816615</t>
-  </si>
-  <si>
-    <t>8721055493211</t>
-  </si>
-  <si>
-    <t>7640158816790</t>
-  </si>
-  <si>
-    <t>7640158816639</t>
-  </si>
-  <si>
-    <t>8721055493884</t>
-  </si>
-  <si>
-    <t>7640158816837</t>
-  </si>
-  <si>
-    <t>7640158816813</t>
-  </si>
-  <si>
-    <t>8721055493853</t>
-  </si>
-  <si>
-    <t>8721055493877</t>
-  </si>
-  <si>
-    <t>8721055493198</t>
-  </si>
-  <si>
-    <t>8721055493228</t>
-  </si>
-  <si>
-    <t>8715658360018</t>
-  </si>
-  <si>
-    <t>8715658370505</t>
-  </si>
-  <si>
-    <t>1840300</t>
-  </si>
-  <si>
-    <t>8715658370062</t>
-  </si>
-  <si>
-    <t>8721055491415</t>
-  </si>
-  <si>
-    <t>8715658360964</t>
-  </si>
-  <si>
-    <t>8719214754105</t>
-  </si>
-  <si>
-    <t>8719214752576</t>
-  </si>
-  <si>
-    <t>6291012878259</t>
-  </si>
-  <si>
-    <t>8715658361428</t>
-  </si>
-  <si>
-    <t>7640158819265</t>
-  </si>
-  <si>
-    <t>8715658998563</t>
-  </si>
-  <si>
-    <t>8715658002512</t>
+    <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
   </si>
   <si>
     <t>8715658380931</t>
   </si>
   <si>
+    <t>Omerta Love Feathers - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658999430</t>
   </si>
   <si>
+    <t>Omerta - Big Release The Mood - EDT men - 100ml</t>
+  </si>
+  <si>
     <t>8715658370086</t>
   </si>
   <si>
+    <t>Omerta - Golden challenge EDT men 100 ml</t>
+  </si>
+  <si>
     <t>8720938379345</t>
   </si>
   <si>
+    <t>Omerta - Invasion - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
     <t>8715658380351</t>
   </si>
   <si>
+    <t>Omerta - Oh So Black For Women - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380221</t>
   </si>
   <si>
+    <t>Omerta - Twice so nice - Eau de parfum - 100ml</t>
+  </si>
+  <si>
     <t>8720938379352</t>
   </si>
   <si>
+    <t>Omerta -Royal X Red- 100ml Eau de Toilette for men</t>
+  </si>
+  <si>
     <t>8715658370369</t>
   </si>
   <si>
+    <t>Omerta Clouds of Love Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658999638</t>
   </si>
   <si>
+    <t>Omerta - Conclude Oud Extreme Attraction - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658370543</t>
   </si>
   <si>
+    <t>Omerta -Ladies World- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380757</t>
   </si>
   <si>
+    <t>Omerta -Lazy Nights- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380405</t>
   </si>
   <si>
+    <t>Omerta -Shoe Red- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380672</t>
   </si>
   <si>
+    <t>Omerta Sensible Man 100ml Eau de Toilette</t>
+  </si>
+  <si>
     <t>8715658999249</t>
   </si>
   <si>
+    <t>Omerta - Love Dust - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380115</t>
   </si>
   <si>
+    <t>Omerta - Express Sensualite Energy - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658998839</t>
   </si>
   <si>
+    <t>Omerta - Golden Challenge Ladies World - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658997993</t>
   </si>
   <si>
+    <t>Omerta -Shoe Blue- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380665</t>
   </si>
   <si>
+    <t>Omerta -Golden Challenge Elixer- 100ml Eau de Toilette for men</t>
+  </si>
+  <si>
     <t>8715658370437</t>
   </si>
   <si>
+    <t>Omerta Invasion Awakening - Vrouwelijke eau de parfum - 100ml</t>
+  </si>
+  <si>
     <t>8715658380658</t>
   </si>
   <si>
+    <t>Omerta - La Donna X - Eau De Parfum - for women - 100ML</t>
+  </si>
+  <si>
     <t>8715658380580</t>
-  </si>
-  <si>
-    <t>6291012002623</t>
-  </si>
-  <si>
-    <t>Real Time - Black Warrior - Eau De Parfum - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658009566</t>
   </si>
 </sst>
 </file>
@@ -711,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -755,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>14.99</v>
@@ -767,671 +830,671 @@
         <v>2.5</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
         <v>12.49</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>13.99</v>
+        <v>13.95</v>
       </c>
       <c r="D3" s="1">
-        <v>13.16</v>
+        <v>13.32</v>
       </c>
       <c r="E3" s="1">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>13.16</v>
+        <v>13.32</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1">
+        <v>14.45</v>
+      </c>
+      <c r="D4" s="1">
+        <v>13.88</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.57</v>
+      </c>
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1">
-        <v>13.55</v>
-      </c>
-      <c r="D4" s="1">
-        <v>12.84</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
       <c r="G4" s="1">
-        <v>12.84</v>
+        <v>13.88</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
-        <v>18.25</v>
+        <v>12.71</v>
       </c>
       <c r="D5" s="1">
-        <v>17.58</v>
+        <v>12.21</v>
       </c>
       <c r="E5" s="1">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>17.58</v>
+        <v>12.21</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>13.95</v>
+        <v>9.95</v>
       </c>
       <c r="D6" s="1">
-        <v>13.33</v>
+        <v>9.48</v>
       </c>
       <c r="E6" s="1">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1">
-        <v>13.33</v>
+        <v>9.48</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
-        <v>13.49</v>
+        <v>12.15</v>
       </c>
       <c r="D7" s="1">
-        <v>12.87</v>
+        <v>11.82</v>
       </c>
       <c r="E7" s="1">
-        <v>0.62</v>
+        <v>0.33</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>12.87</v>
+        <v>11.82</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1">
-        <v>12.89</v>
+        <v>5.25</v>
       </c>
       <c r="D8" s="1">
-        <v>12.29</v>
+        <v>4.99</v>
       </c>
       <c r="E8" s="1">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G8" s="1">
-        <v>12.29</v>
+        <v>4.99</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1">
-        <v>12.49</v>
+        <v>5.25</v>
       </c>
       <c r="D9" s="1">
-        <v>11.97</v>
+        <v>4.99</v>
       </c>
       <c r="E9" s="1">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1">
-        <v>11.97</v>
+        <v>4.99</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1">
-        <v>12</v>
+        <v>5.25</v>
       </c>
       <c r="D10" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="E10" s="1">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G10" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1">
-        <v>9.95</v>
+        <v>5.25</v>
       </c>
       <c r="D11" s="1">
-        <v>9.48</v>
+        <v>4.99</v>
       </c>
       <c r="E11" s="1">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G11" s="1">
-        <v>9.48</v>
+        <v>4.99</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1">
-        <v>12.75</v>
+        <v>5.25</v>
       </c>
       <c r="D12" s="1">
-        <v>12.29</v>
+        <v>4.99</v>
       </c>
       <c r="E12" s="1">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G12" s="1">
-        <v>12.29</v>
+        <v>4.99</v>
       </c>
       <c r="H12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D13" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="1">
-        <v>11.95</v>
-      </c>
-      <c r="D13" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
       <c r="G13" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1">
-        <v>12.89</v>
+        <v>5.25</v>
       </c>
       <c r="D14" s="1">
-        <v>12.48</v>
+        <v>4.99</v>
       </c>
       <c r="E14" s="1">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G14" s="1">
-        <v>12.48</v>
+        <v>4.99</v>
       </c>
       <c r="H14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1">
-        <v>12.89</v>
+        <v>5.25</v>
       </c>
       <c r="D15" s="1">
-        <v>12.48</v>
+        <v>4.99</v>
       </c>
       <c r="E15" s="1">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G15" s="1">
-        <v>12.48</v>
+        <v>4.99</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1">
-        <v>12.09</v>
+        <v>5.25</v>
       </c>
       <c r="D16" s="1">
-        <v>11.69</v>
+        <v>4.99</v>
       </c>
       <c r="E16" s="1">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G16" s="1">
-        <v>11.69</v>
+        <v>4.99</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1">
-        <v>12.15</v>
+        <v>5.25</v>
       </c>
       <c r="D17" s="1">
-        <v>11.76</v>
+        <v>4.99</v>
       </c>
       <c r="E17" s="1">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G17" s="1">
-        <v>11.76</v>
+        <v>4.99</v>
       </c>
       <c r="H17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1">
-        <v>11.89</v>
+        <v>5.25</v>
       </c>
       <c r="D18" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="E18" s="1">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G18" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="H18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1">
-        <v>15.89</v>
+        <v>5.25</v>
       </c>
       <c r="D19" s="1">
-        <v>15.5</v>
+        <v>4.99</v>
       </c>
       <c r="E19" s="1">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G19" s="1">
-        <v>15.5</v>
+        <v>4.99</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1">
-        <v>12.75</v>
+        <v>5.25</v>
       </c>
       <c r="D20" s="1">
-        <v>12.38</v>
+        <v>4.99</v>
       </c>
       <c r="E20" s="1">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G20" s="1">
-        <v>12.38</v>
+        <v>4.99</v>
       </c>
       <c r="H20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1">
-        <v>13.49</v>
+        <v>5.25</v>
       </c>
       <c r="D21" s="1">
-        <v>13.15</v>
+        <v>4.99</v>
       </c>
       <c r="E21" s="1">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G21" s="1">
-        <v>13.15</v>
+        <v>4.99</v>
       </c>
       <c r="H21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1">
-        <v>12.59</v>
+        <v>5.25</v>
       </c>
       <c r="D22" s="1">
-        <v>12.27</v>
+        <v>4.99</v>
       </c>
       <c r="E22" s="1">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G22" s="1">
-        <v>12.27</v>
+        <v>4.99</v>
       </c>
       <c r="H22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1">
-        <v>12.69</v>
+        <v>12.87</v>
       </c>
       <c r="D23" s="1">
-        <v>12.37</v>
+        <v>12.61</v>
       </c>
       <c r="E23" s="1">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G23" s="1">
-        <v>12.37</v>
+        <v>12.61</v>
       </c>
       <c r="H23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1">
-        <v>13.15</v>
+        <v>5.25</v>
       </c>
       <c r="D24" s="1">
-        <v>12.84</v>
+        <v>4.99</v>
       </c>
       <c r="E24" s="1">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G24" s="1">
-        <v>12.84</v>
+        <v>4.99</v>
       </c>
       <c r="H24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1">
-        <v>12.89</v>
+        <v>5.25</v>
       </c>
       <c r="D25" s="1">
-        <v>12.59</v>
+        <v>4.99</v>
       </c>
       <c r="E25" s="1">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G25" s="1">
-        <v>12.59</v>
+        <v>4.99</v>
       </c>
       <c r="H25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C26" s="1">
-        <v>11.79</v>
+        <v>5.25</v>
       </c>
       <c r="D26" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="E26" s="1">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G26" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1">
-        <v>14.5</v>
+        <v>5.25</v>
       </c>
       <c r="D27" s="1">
-        <v>14.21</v>
+        <v>4.99</v>
       </c>
       <c r="E27" s="1">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G27" s="1">
-        <v>14.21</v>
+        <v>4.99</v>
       </c>
       <c r="H27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1">
         <v>5.25</v>
@@ -1443,21 +1506,21 @@
         <v>0.26</v>
       </c>
       <c r="F28" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="G28" s="1">
         <v>4.99</v>
       </c>
       <c r="H28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1">
         <v>5.25</v>
@@ -1469,1417 +1532,715 @@
         <v>0.26</v>
       </c>
       <c r="F29" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="G29" s="1">
         <v>4.99</v>
       </c>
       <c r="H29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D30" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E30" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F30" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G30" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C31" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D31" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E31" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F31" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G31" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C32" s="1">
-        <v>5.25</v>
+        <v>11.69</v>
       </c>
       <c r="D32" s="1">
-        <v>4.99</v>
+        <v>11.5</v>
       </c>
       <c r="E32" s="1">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="G32" s="1">
-        <v>4.99</v>
+        <v>11.5</v>
       </c>
       <c r="H32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C33" s="1">
-        <v>5.25</v>
+        <v>13.79</v>
       </c>
       <c r="D33" s="1">
-        <v>4.99</v>
+        <v>13.63</v>
       </c>
       <c r="E33" s="1">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="F33" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="G33" s="1">
-        <v>4.99</v>
+        <v>13.63</v>
       </c>
       <c r="H33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C34" s="1">
-        <v>5.25</v>
+        <v>12.35</v>
       </c>
       <c r="D34" s="1">
-        <v>4.99</v>
+        <v>12.21</v>
       </c>
       <c r="E34" s="1">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="F34" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1">
-        <v>4.99</v>
+        <v>12.21</v>
       </c>
       <c r="H34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C35" s="1">
-        <v>5.25</v>
+        <v>11.97</v>
       </c>
       <c r="D35" s="1">
-        <v>4.99</v>
+        <v>11.87</v>
       </c>
       <c r="E35" s="1">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="F35" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="G35" s="1">
-        <v>4.99</v>
+        <v>11.87</v>
       </c>
       <c r="H35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C36" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D36" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E36" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G36" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D37" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E37" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G37" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D38" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E38" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G38" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="C39" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D39" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E39" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G39" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C40" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D40" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E40" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G40" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D41" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E41" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G41" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="C42" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D42" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E42" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G42" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="C43" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D43" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E43" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G43" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D44" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E44" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G44" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="C45" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D45" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E45" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G45" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D46" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E46" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G46" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D47" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E47" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G47" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D48" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E48" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="G48" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H48" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1">
-        <v>11.75</v>
+        <v>9.99</v>
       </c>
       <c r="D49" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="E49" s="1">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="G49" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="H49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1">
         <v>9.99</v>
       </c>
       <c r="D50" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="E50" s="1">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="F50" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G50" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="H50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1">
         <v>9.99</v>
       </c>
       <c r="D51" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="E51" s="1">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="F51" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G51" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="H51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="C52" s="1">
-        <v>14.95</v>
+        <v>9.99</v>
       </c>
       <c r="D52" s="1">
-        <v>14.74</v>
+        <v>9.95</v>
       </c>
       <c r="E52" s="1">
-        <v>0.21</v>
+        <v>0.04</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="G52" s="1">
-        <v>14.74</v>
+        <v>9.95</v>
       </c>
       <c r="H52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D53" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F53" t="s">
         <v>71</v>
       </c>
-      <c r="B53" t="s">
-        <v>71</v>
-      </c>
-      <c r="C53" s="1">
-        <v>14.25</v>
-      </c>
-      <c r="D53" s="1">
-        <v>14.05</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="F53" t="s">
-        <v>12</v>
-      </c>
       <c r="G53" s="1">
-        <v>14.05</v>
+        <v>9.95</v>
       </c>
       <c r="H53" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="C54" s="1">
-        <v>11.69</v>
+        <v>9.99</v>
       </c>
       <c r="D54" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="E54" s="1">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="F54" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="G54" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="H54" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="C55" s="1">
-        <v>12.5</v>
+        <v>9.99</v>
       </c>
       <c r="D55" s="1">
-        <v>12.33</v>
+        <v>9.95</v>
       </c>
       <c r="E55" s="1">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="F55" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="G55" s="1">
-        <v>12.33</v>
+        <v>9.95</v>
       </c>
       <c r="H55" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="C56" s="1">
-        <v>12.55</v>
+        <v>9.99</v>
       </c>
       <c r="D56" s="1">
-        <v>12.38</v>
+        <v>9.95</v>
       </c>
       <c r="E56" s="1">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="G56" s="1">
-        <v>12.38</v>
+        <v>9.95</v>
       </c>
       <c r="H56" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>75</v>
-      </c>
-      <c r="B57" t="s">
-        <v>75</v>
-      </c>
-      <c r="C57" s="1">
-        <v>12.75</v>
-      </c>
-      <c r="D57" s="1">
-        <v>12.59</v>
-      </c>
-      <c r="E57" s="1">
-        <v>0.16</v>
-      </c>
-      <c r="F57" t="s">
-        <v>12</v>
-      </c>
-      <c r="G57" s="1">
-        <v>12.59</v>
-      </c>
-      <c r="H57" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>76</v>
-      </c>
-      <c r="B58" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" s="1">
-        <v>12.75</v>
-      </c>
-      <c r="D58" s="1">
-        <v>12.59</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0.16</v>
-      </c>
-      <c r="F58" t="s">
-        <v>12</v>
-      </c>
-      <c r="G58" s="1">
-        <v>12.59</v>
-      </c>
-      <c r="H58" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>77</v>
-      </c>
-      <c r="B59" t="s">
-        <v>77</v>
-      </c>
-      <c r="C59" s="1">
-        <v>13.09</v>
-      </c>
-      <c r="D59" s="1">
-        <v>12.99</v>
-      </c>
-      <c r="E59" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F59" t="s">
-        <v>12</v>
-      </c>
-      <c r="G59" s="1">
-        <v>12.99</v>
-      </c>
-      <c r="H59" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>78</v>
-      </c>
-      <c r="B60" t="s">
-        <v>78</v>
-      </c>
-      <c r="C60" s="1">
-        <v>12.19</v>
-      </c>
-      <c r="D60" s="1">
-        <v>12.14</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" s="1">
-        <v>12.14</v>
-      </c>
-      <c r="H60" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>79</v>
-      </c>
-      <c r="B61" t="s">
-        <v>79</v>
-      </c>
-      <c r="C61" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D61" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E61" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F61" t="s">
-        <v>68</v>
-      </c>
-      <c r="G61" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H61" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>80</v>
-      </c>
-      <c r="B62" t="s">
-        <v>80</v>
-      </c>
-      <c r="C62" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D62" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F62" t="s">
-        <v>68</v>
-      </c>
-      <c r="G62" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H62" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>81</v>
-      </c>
-      <c r="B63" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D63" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F63" t="s">
-        <v>68</v>
-      </c>
-      <c r="G63" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H63" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>82</v>
-      </c>
-      <c r="B64" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D64" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F64" t="s">
-        <v>68</v>
-      </c>
-      <c r="G64" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H64" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>83</v>
-      </c>
-      <c r="B65" t="s">
-        <v>83</v>
-      </c>
-      <c r="C65" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D65" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F65" t="s">
-        <v>68</v>
-      </c>
-      <c r="G65" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H65" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>84</v>
-      </c>
-      <c r="B66" t="s">
-        <v>84</v>
-      </c>
-      <c r="C66" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D66" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F66" t="s">
-        <v>68</v>
-      </c>
-      <c r="G66" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>85</v>
-      </c>
-      <c r="B67" t="s">
-        <v>85</v>
-      </c>
-      <c r="C67" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D67" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G67" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H67" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>86</v>
-      </c>
-      <c r="B68" t="s">
-        <v>86</v>
-      </c>
-      <c r="C68" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D68" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F68" t="s">
-        <v>68</v>
-      </c>
-      <c r="G68" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H68" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>87</v>
-      </c>
-      <c r="B69" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D69" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E69" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F69" t="s">
-        <v>68</v>
-      </c>
-      <c r="G69" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H69" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>88</v>
-      </c>
-      <c r="B70" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D70" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F70" t="s">
-        <v>68</v>
-      </c>
-      <c r="G70" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H70" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>89</v>
-      </c>
-      <c r="B71" t="s">
-        <v>89</v>
-      </c>
-      <c r="C71" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D71" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F71" t="s">
-        <v>68</v>
-      </c>
-      <c r="G71" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H71" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>90</v>
-      </c>
-      <c r="B72" t="s">
-        <v>90</v>
-      </c>
-      <c r="C72" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D72" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E72" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F72" t="s">
-        <v>68</v>
-      </c>
-      <c r="G72" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H72" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>91</v>
-      </c>
-      <c r="B73" t="s">
-        <v>91</v>
-      </c>
-      <c r="C73" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D73" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E73" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F73" t="s">
-        <v>68</v>
-      </c>
-      <c r="G73" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H73" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>92</v>
-      </c>
-      <c r="B74" t="s">
-        <v>92</v>
-      </c>
-      <c r="C74" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D74" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E74" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F74" t="s">
-        <v>68</v>
-      </c>
-      <c r="G74" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H74" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>93</v>
-      </c>
-      <c r="B75" t="s">
-        <v>93</v>
-      </c>
-      <c r="C75" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D75" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E75" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F75" t="s">
-        <v>68</v>
-      </c>
-      <c r="G75" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H75" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>94</v>
-      </c>
-      <c r="B76" t="s">
-        <v>94</v>
-      </c>
-      <c r="C76" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D76" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E76" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F76" t="s">
-        <v>68</v>
-      </c>
-      <c r="G76" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H76" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>95</v>
-      </c>
-      <c r="B77" t="s">
-        <v>95</v>
-      </c>
-      <c r="C77" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D77" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E77" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F77" t="s">
-        <v>68</v>
-      </c>
-      <c r="G77" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H77" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>96</v>
-      </c>
-      <c r="B78" t="s">
-        <v>96</v>
-      </c>
-      <c r="C78" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D78" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E78" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F78" t="s">
-        <v>68</v>
-      </c>
-      <c r="G78" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H78" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>97</v>
-      </c>
-      <c r="B79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C79" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D79" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F79" t="s">
-        <v>68</v>
-      </c>
-      <c r="G79" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H79" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>98</v>
-      </c>
-      <c r="B80" t="s">
-        <v>98</v>
-      </c>
-      <c r="C80" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D80" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E80" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F80" t="s">
-        <v>68</v>
-      </c>
-      <c r="G80" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H80" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>99</v>
-      </c>
-      <c r="B81" t="s">
-        <v>99</v>
-      </c>
-      <c r="C81" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D81" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E81" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F81" t="s">
-        <v>68</v>
-      </c>
-      <c r="G81" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H81" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>100</v>
-      </c>
-      <c r="B82" t="s">
-        <v>100</v>
-      </c>
-      <c r="C82" s="1">
-        <v>12.39</v>
-      </c>
-      <c r="D82" s="1">
-        <v>12.37</v>
-      </c>
-      <c r="E82" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="F82" t="s">
-        <v>12</v>
-      </c>
-      <c r="G82" s="1">
-        <v>12.37</v>
-      </c>
-      <c r="H82" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>101</v>
-      </c>
-      <c r="B83" t="s">
-        <v>102</v>
-      </c>
-      <c r="C83" s="1">
-        <v>12.15</v>
-      </c>
-      <c r="D83" s="1">
-        <v>12.14</v>
-      </c>
-      <c r="E83" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="F83" t="s">
-        <v>12</v>
-      </c>
-      <c r="G83" s="1">
-        <v>12.14</v>
-      </c>
-      <c r="H83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/prijsrapport-2026-04-12.xlsx
+++ b/rapporten/prijsrapport-2026-04-12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="116">
   <si>
     <t>Product</t>
   </si>
@@ -49,27 +49,15 @@
     <t>FBR</t>
   </si>
   <si>
-    <t>Hello Kitty You're Cute Eau de Parfum voor Kinderen 50ml</t>
-  </si>
-  <si>
-    <t>8721055493303</t>
+    <t>Hello Kitty - Giftset - Kisses - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>8721055493440</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
   </si>
   <si>
-    <t>Hello Kitty Giftset 3 x 15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158817032</t>
-  </si>
-  <si>
-    <t>Omerta - Ma Merveilleuse - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658997443</t>
-  </si>
-  <si>
     <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
   </si>
   <si>
@@ -79,10 +67,10 @@
     <t>Juwelium</t>
   </si>
   <si>
-    <t>Real Time - Black Warrior - Eau De Parfum - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658009566</t>
+    <t>Creation Lamis Diable Bleu parfum - Oriëntaalse en houtige eau de parfum voor dames</t>
+  </si>
+  <si>
+    <t>5414666001366</t>
   </si>
   <si>
     <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
@@ -178,12 +166,6 @@
     <t>8721055493884</t>
   </si>
   <si>
-    <t>Hello Kitty - Giftset - Kisses - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>8721055493440</t>
-  </si>
-  <si>
     <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
   </si>
   <si>
@@ -235,16 +217,10 @@
     <t>8715658370062</t>
   </si>
   <si>
-    <t>Bubble Bliss Unicorn Giftbook Parfum Dreamy Glitterwings EDP voor meisjes 50ml</t>
-  </si>
-  <si>
-    <t>8721055492245</t>
-  </si>
-  <si>
-    <t>Dorall Twilight Wilderness - Herenparfum eau de toilette - 100 ml</t>
-  </si>
-  <si>
-    <t>6291012874381</t>
+    <t>Real Time - Fine Gold Pink Vibrations - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658361015</t>
   </si>
   <si>
     <t>Creation Lamis Golden Wave for Men Giftset</t>
@@ -253,10 +229,10 @@
     <t>6291012002661</t>
   </si>
   <si>
-    <t>Real Time Hunted For Men - eau de toilette voor heren - 100ML</t>
-  </si>
-  <si>
-    <t>8715658350521</t>
+    <t>Real Time - Out Of Order - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658350033</t>
   </si>
   <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
@@ -774,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -847,19 +823,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>13.95</v>
+        <v>12.61</v>
       </c>
       <c r="D3" s="1">
-        <v>13.32</v>
+        <v>12.09</v>
       </c>
       <c r="E3" s="1">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>13.32</v>
+        <v>12.09</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -873,19 +849,19 @@
         <v>16</v>
       </c>
       <c r="C4" s="1">
-        <v>14.45</v>
+        <v>9.95</v>
       </c>
       <c r="D4" s="1">
-        <v>13.88</v>
+        <v>9.48</v>
       </c>
       <c r="E4" s="1">
-        <v>0.57</v>
+        <v>0.47</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1">
-        <v>13.88</v>
+        <v>9.48</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -893,25 +869,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1">
-        <v>12.71</v>
+        <v>12.95</v>
       </c>
       <c r="D5" s="1">
-        <v>12.21</v>
+        <v>12.59</v>
       </c>
       <c r="E5" s="1">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>12.21</v>
+        <v>12.59</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -919,25 +895,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
-        <v>9.95</v>
+        <v>5.25</v>
       </c>
       <c r="D6" s="1">
-        <v>9.48</v>
+        <v>4.99</v>
       </c>
       <c r="E6" s="1">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1">
-        <v>9.48</v>
+        <v>4.99</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -945,25 +921,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D7" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1">
-        <v>12.15</v>
-      </c>
-      <c r="D7" s="1">
-        <v>11.82</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
       <c r="G7" s="1">
-        <v>11.82</v>
+        <v>4.99</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -971,10 +947,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1">
         <v>5.25</v>
@@ -986,7 +962,7 @@
         <v>0.26</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G8" s="1">
         <v>4.99</v>
@@ -1012,7 +988,7 @@
         <v>0.26</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G9" s="1">
         <v>4.99</v>
@@ -1038,7 +1014,7 @@
         <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1">
         <v>4.99</v>
@@ -1064,7 +1040,7 @@
         <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1">
         <v>4.99</v>
@@ -1090,7 +1066,7 @@
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
@@ -1116,7 +1092,7 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
@@ -1142,7 +1118,7 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
@@ -1168,7 +1144,7 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
@@ -1194,7 +1170,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
@@ -1220,7 +1196,7 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
@@ -1246,7 +1222,7 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
@@ -1272,7 +1248,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1298,7 +1274,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1324,7 +1300,7 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
@@ -1350,7 +1326,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1367,19 +1343,19 @@
         <v>56</v>
       </c>
       <c r="C23" s="1">
-        <v>12.87</v>
+        <v>5.25</v>
       </c>
       <c r="D23" s="1">
-        <v>12.61</v>
+        <v>4.99</v>
       </c>
       <c r="E23" s="1">
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G23" s="1">
-        <v>12.61</v>
+        <v>4.99</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -1402,7 +1378,7 @@
         <v>0.26</v>
       </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G24" s="1">
         <v>4.99</v>
@@ -1428,7 +1404,7 @@
         <v>0.26</v>
       </c>
       <c r="F25" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G25" s="1">
         <v>4.99</v>
@@ -1454,7 +1430,7 @@
         <v>0.26</v>
       </c>
       <c r="F26" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G26" s="1">
         <v>4.99</v>
@@ -1471,19 +1447,19 @@
         <v>64</v>
       </c>
       <c r="C27" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D27" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E27" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F27" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="G27" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
@@ -1491,25 +1467,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D28" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E28" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F28" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="G28" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
@@ -1517,25 +1493,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" s="1">
-        <v>5.25</v>
+        <v>11.69</v>
       </c>
       <c r="D29" s="1">
-        <v>4.99</v>
+        <v>11.5</v>
       </c>
       <c r="E29" s="1">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="F29" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G29" s="1">
-        <v>4.99</v>
+        <v>11.5</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
@@ -1543,25 +1519,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="1">
-        <v>9.99</v>
+        <v>12.21</v>
       </c>
       <c r="D30" s="1">
-        <v>9.75</v>
+        <v>12.14</v>
       </c>
       <c r="E30" s="1">
-        <v>0.24</v>
+        <v>0.07</v>
       </c>
       <c r="F30" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="G30" s="1">
-        <v>9.75</v>
+        <v>12.14</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -1575,19 +1551,19 @@
         <v>73</v>
       </c>
       <c r="C31" s="1">
-        <v>9.99</v>
+        <v>12.89</v>
       </c>
       <c r="D31" s="1">
-        <v>9.75</v>
+        <v>12.84</v>
       </c>
       <c r="E31" s="1">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="F31" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="G31" s="1">
-        <v>9.75</v>
+        <v>12.84</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -1601,19 +1577,19 @@
         <v>75</v>
       </c>
       <c r="C32" s="1">
-        <v>11.69</v>
+        <v>9.99</v>
       </c>
       <c r="D32" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="E32" s="1">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="G32" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -1627,19 +1603,19 @@
         <v>77</v>
       </c>
       <c r="C33" s="1">
-        <v>13.79</v>
+        <v>9.99</v>
       </c>
       <c r="D33" s="1">
-        <v>13.63</v>
+        <v>9.95</v>
       </c>
       <c r="E33" s="1">
-        <v>0.16</v>
+        <v>0.04</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="G33" s="1">
-        <v>13.63</v>
+        <v>9.95</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -1653,19 +1629,19 @@
         <v>79</v>
       </c>
       <c r="C34" s="1">
-        <v>12.35</v>
+        <v>9.99</v>
       </c>
       <c r="D34" s="1">
-        <v>12.21</v>
+        <v>9.95</v>
       </c>
       <c r="E34" s="1">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="G34" s="1">
-        <v>12.21</v>
+        <v>9.95</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -1679,19 +1655,19 @@
         <v>81</v>
       </c>
       <c r="C35" s="1">
-        <v>11.97</v>
+        <v>9.99</v>
       </c>
       <c r="D35" s="1">
-        <v>11.87</v>
+        <v>9.95</v>
       </c>
       <c r="E35" s="1">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="G35" s="1">
-        <v>11.87</v>
+        <v>9.95</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -1714,7 +1690,7 @@
         <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G36" s="1">
         <v>9.95</v>
@@ -1740,7 +1716,7 @@
         <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G37" s="1">
         <v>9.95</v>
@@ -1766,7 +1742,7 @@
         <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G38" s="1">
         <v>9.95</v>
@@ -1792,7 +1768,7 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
@@ -1818,7 +1794,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
@@ -1844,7 +1820,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1870,7 +1846,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1896,7 +1872,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1922,7 +1898,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1948,7 +1924,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -1974,7 +1950,7 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
@@ -2000,7 +1976,7 @@
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G47" s="1">
         <v>9.95</v>
@@ -2026,7 +2002,7 @@
         <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G48" s="1">
         <v>9.95</v>
@@ -2052,7 +2028,7 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
@@ -2078,7 +2054,7 @@
         <v>0.04</v>
       </c>
       <c r="F50" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G50" s="1">
         <v>9.95</v>
@@ -2104,7 +2080,7 @@
         <v>0.04</v>
       </c>
       <c r="F51" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G51" s="1">
         <v>9.95</v>
@@ -2130,116 +2106,12 @@
         <v>0.04</v>
       </c>
       <c r="F52" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G52" s="1">
         <v>9.95</v>
       </c>
       <c r="H52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>116</v>
-      </c>
-      <c r="B53" t="s">
-        <v>117</v>
-      </c>
-      <c r="C53" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D53" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F53" t="s">
-        <v>71</v>
-      </c>
-      <c r="G53" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>118</v>
-      </c>
-      <c r="B54" t="s">
-        <v>119</v>
-      </c>
-      <c r="C54" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D54" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E54" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F54" t="s">
-        <v>71</v>
-      </c>
-      <c r="G54" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>120</v>
-      </c>
-      <c r="B55" t="s">
-        <v>121</v>
-      </c>
-      <c r="C55" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D55" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E55" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F55" t="s">
-        <v>71</v>
-      </c>
-      <c r="G55" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" t="s">
-        <v>123</v>
-      </c>
-      <c r="C56" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D56" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F56" t="s">
-        <v>71</v>
-      </c>
-      <c r="G56" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H56" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-04-12.xlsx
+++ b/rapporten/prijsrapport-2026-04-12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="130">
   <si>
     <t>Product</t>
   </si>
@@ -49,184 +49,226 @@
     <t>FBR</t>
   </si>
   <si>
+    <t>Omerta - Red Class Elixir de Luxe - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658370574</t>
+  </si>
+  <si>
+    <t>Koopjesfun.nl</t>
+  </si>
+  <si>
+    <t>Bubble Bliss Flamingo Giftbook Parfum Pink &amp; Proud EDP voor meisjes 50ml</t>
+  </si>
+  <si>
+    <t>8721055492184</t>
+  </si>
+  <si>
+    <t>Creation Lamis Golden Wave for Men Giftset</t>
+  </si>
+  <si>
+    <t>6291012002661</t>
+  </si>
+  <si>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
+    <t>5414666014427</t>
+  </si>
+  <si>
+    <t>Juwelium</t>
+  </si>
+  <si>
+    <t>Real Time - Please Call Me - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658360971</t>
+  </si>
+  <si>
+    <t>Real Time Love You Red 100 ml - Eau de Parfum - Damesparfum</t>
+  </si>
+  <si>
+    <t>8715658360056</t>
+  </si>
+  <si>
+    <t>Real Time Hunted For Men - eau de toilette voor heren - 100ML</t>
+  </si>
+  <si>
+    <t>8715658350521</t>
+  </si>
+  <si>
+    <t>NG -Next Fragranse For Her- 100ml Eau de Parfum-50ml Showergel-50ml Bodylotion</t>
+  </si>
+  <si>
+    <t>8719214755829</t>
+  </si>
+  <si>
+    <t>SENTIO FEESTDAGEN PINK - Family Magical - Eau de Parfum 50ml</t>
+  </si>
+  <si>
+    <t>8721055492740</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493860</t>
+  </si>
+  <si>
+    <t>Minimarkt W&amp;M</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494225</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494263</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816691</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816677</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816653</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494270</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494232</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Sparkle- Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493891</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816714</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816615</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493211</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816790</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816639</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493884</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816837</t>
+  </si>
+  <si>
+    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816813</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Smile - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493853</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Shine - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493877</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493198</t>
+  </si>
+  <si>
+    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493228</t>
+  </si>
+  <si>
+    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658370505</t>
+  </si>
+  <si>
+    <t>Bliksma Retail B.V.</t>
+  </si>
+  <si>
+    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
+  </si>
+  <si>
+    <t>8715658370062</t>
+  </si>
+  <si>
+    <t>SENTIO FEESTDAGEN PINK - Holly Jolly Magic - Eau de Parfum 50ml</t>
+  </si>
+  <si>
+    <t>8721055492719</t>
+  </si>
+  <si>
+    <t>Sentio Happy Birthday Giftset - Luxe parfum en showergel voor iedereen</t>
+  </si>
+  <si>
+    <t>8721055494140</t>
+  </si>
+  <si>
     <t>Hello Kitty - Giftset - Kisses - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
   </si>
   <si>
     <t>8721055493440</t>
-  </si>
-  <si>
-    <t>Koopjesfun.nl</t>
-  </si>
-  <si>
-    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
-  </si>
-  <si>
-    <t>5414666014427</t>
-  </si>
-  <si>
-    <t>Juwelium</t>
-  </si>
-  <si>
-    <t>Creation Lamis Diable Bleu parfum - Oriëntaalse en houtige eau de parfum voor dames</t>
-  </si>
-  <si>
-    <t>5414666001366</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493860</t>
-  </si>
-  <si>
-    <t>Minimarkt W&amp;M</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494225</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494263</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816691</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816677</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816653</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494270</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494232</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Sparkle- Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493891</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816714</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816615</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8721055493211</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816790</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816639</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493884</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816837</t>
-  </si>
-  <si>
-    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816813</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Smile - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493853</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Shine - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493877</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8721055493198</t>
-  </si>
-  <si>
-    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8721055493228</t>
-  </si>
-  <si>
-    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370505</t>
-  </si>
-  <si>
-    <t>Bliksma Retail B.V.</t>
-  </si>
-  <si>
-    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>8715658370062</t>
-  </si>
-  <si>
-    <t>Real Time - Fine Gold Pink Vibrations - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658361015</t>
-  </si>
-  <si>
-    <t>Creation Lamis Golden Wave for Men Giftset</t>
-  </si>
-  <si>
-    <t>6291012002661</t>
   </si>
   <si>
     <t>Real Time - Out Of Order - Eau De Toilette - 100ML</t>
@@ -750,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -823,19 +865,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>12.61</v>
+        <v>13.15</v>
       </c>
       <c r="D3" s="1">
-        <v>12.09</v>
+        <v>12.38</v>
       </c>
       <c r="E3" s="1">
-        <v>0.52</v>
+        <v>0.77</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>12.09</v>
+        <v>12.38</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -849,19 +891,19 @@
         <v>16</v>
       </c>
       <c r="C4" s="1">
-        <v>9.95</v>
+        <v>12.95</v>
       </c>
       <c r="D4" s="1">
-        <v>9.48</v>
+        <v>12.24</v>
       </c>
       <c r="E4" s="1">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>9.48</v>
+        <v>12.24</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -869,25 +911,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
       <c r="C5" s="1">
-        <v>12.95</v>
+        <v>12.14</v>
       </c>
       <c r="D5" s="1">
-        <v>12.59</v>
+        <v>11.62</v>
       </c>
       <c r="E5" s="1">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>12.59</v>
+        <v>11.62</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -895,25 +937,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="D6" s="1">
+        <v>9.48</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="F6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="D6" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
       <c r="G6" s="1">
-        <v>4.99</v>
+        <v>9.48</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -921,25 +963,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
       <c r="C7" s="1">
-        <v>5.25</v>
+        <v>13.95</v>
       </c>
       <c r="D7" s="1">
-        <v>4.99</v>
+        <v>13.56</v>
       </c>
       <c r="E7" s="1">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>4.99</v>
+        <v>13.56</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -947,25 +989,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
       <c r="C8" s="1">
-        <v>5.25</v>
+        <v>12.45</v>
       </c>
       <c r="D8" s="1">
-        <v>4.99</v>
+        <v>12.07</v>
       </c>
       <c r="E8" s="1">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>4.99</v>
+        <v>12.07</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -973,25 +1015,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
       <c r="C9" s="1">
-        <v>5.25</v>
+        <v>11.87</v>
       </c>
       <c r="D9" s="1">
-        <v>4.99</v>
+        <v>11.5</v>
       </c>
       <c r="E9" s="1">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1">
-        <v>4.99</v>
+        <v>11.5</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -999,25 +1041,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
       <c r="C10" s="1">
-        <v>5.25</v>
+        <v>13.45</v>
       </c>
       <c r="D10" s="1">
-        <v>4.99</v>
+        <v>13.09</v>
       </c>
       <c r="E10" s="1">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G10" s="1">
-        <v>4.99</v>
+        <v>13.09</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -1025,25 +1067,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
       <c r="C11" s="1">
-        <v>5.25</v>
+        <v>14.95</v>
       </c>
       <c r="D11" s="1">
-        <v>4.99</v>
+        <v>14.6</v>
       </c>
       <c r="E11" s="1">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G11" s="1">
-        <v>4.99</v>
+        <v>14.6</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
@@ -1051,10 +1093,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
         <v>33</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
       </c>
       <c r="C12" s="1">
         <v>5.25</v>
@@ -1066,7 +1108,7 @@
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
@@ -1092,7 +1134,7 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
@@ -1118,7 +1160,7 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
@@ -1144,7 +1186,7 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
@@ -1170,7 +1212,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
@@ -1196,7 +1238,7 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
@@ -1222,7 +1264,7 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
@@ -1248,7 +1290,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1274,7 +1316,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1300,7 +1342,7 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
@@ -1326,7 +1368,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1352,7 +1394,7 @@
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
@@ -1378,7 +1420,7 @@
         <v>0.26</v>
       </c>
       <c r="F24" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G24" s="1">
         <v>4.99</v>
@@ -1404,7 +1446,7 @@
         <v>0.26</v>
       </c>
       <c r="F25" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G25" s="1">
         <v>4.99</v>
@@ -1430,7 +1472,7 @@
         <v>0.26</v>
       </c>
       <c r="F26" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G26" s="1">
         <v>4.99</v>
@@ -1447,19 +1489,19 @@
         <v>64</v>
       </c>
       <c r="C27" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D27" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E27" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="G27" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
@@ -1467,25 +1509,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" t="s">
         <v>66</v>
       </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
       <c r="C28" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D28" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E28" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="G28" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
@@ -1493,25 +1535,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
         <v>68</v>
       </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
       <c r="C29" s="1">
-        <v>11.69</v>
+        <v>5.25</v>
       </c>
       <c r="D29" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="E29" s="1">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G29" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
@@ -1519,25 +1561,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" t="s">
         <v>70</v>
       </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
       <c r="C30" s="1">
-        <v>12.21</v>
+        <v>5.25</v>
       </c>
       <c r="D30" s="1">
-        <v>12.14</v>
+        <v>4.99</v>
       </c>
       <c r="E30" s="1">
-        <v>0.07</v>
+        <v>0.26</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G30" s="1">
-        <v>12.14</v>
+        <v>4.99</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -1545,25 +1587,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
       <c r="C31" s="1">
-        <v>12.89</v>
+        <v>5.25</v>
       </c>
       <c r="D31" s="1">
-        <v>12.84</v>
+        <v>4.99</v>
       </c>
       <c r="E31" s="1">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G31" s="1">
-        <v>12.84</v>
+        <v>4.99</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -1571,25 +1613,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
         <v>74</v>
       </c>
-      <c r="B32" t="s">
-        <v>75</v>
-      </c>
       <c r="C32" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D32" s="1">
-        <v>9.95</v>
+        <v>4.99</v>
       </c>
       <c r="E32" s="1">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="F32" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="G32" s="1">
-        <v>9.95</v>
+        <v>4.99</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -1597,25 +1639,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" t="s">
         <v>76</v>
-      </c>
-      <c r="B33" t="s">
-        <v>77</v>
       </c>
       <c r="C33" s="1">
         <v>9.99</v>
       </c>
       <c r="D33" s="1">
-        <v>9.95</v>
+        <v>9.75</v>
       </c>
       <c r="E33" s="1">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G33" s="1">
-        <v>9.95</v>
+        <v>9.75</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -1632,16 +1674,16 @@
         <v>9.99</v>
       </c>
       <c r="D34" s="1">
-        <v>9.95</v>
+        <v>9.75</v>
       </c>
       <c r="E34" s="1">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="F34" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G34" s="1">
-        <v>9.95</v>
+        <v>9.75</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -1655,19 +1697,19 @@
         <v>81</v>
       </c>
       <c r="C35" s="1">
-        <v>9.99</v>
+        <v>13.99</v>
       </c>
       <c r="D35" s="1">
-        <v>9.95</v>
+        <v>13.76</v>
       </c>
       <c r="E35" s="1">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="G35" s="1">
-        <v>9.95</v>
+        <v>13.76</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -1681,19 +1723,19 @@
         <v>83</v>
       </c>
       <c r="C36" s="1">
-        <v>9.99</v>
+        <v>14.99</v>
       </c>
       <c r="D36" s="1">
-        <v>9.95</v>
+        <v>14.78</v>
       </c>
       <c r="E36" s="1">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="G36" s="1">
-        <v>9.95</v>
+        <v>14.78</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -1707,19 +1749,19 @@
         <v>85</v>
       </c>
       <c r="C37" s="1">
-        <v>9.99</v>
+        <v>12.09</v>
       </c>
       <c r="D37" s="1">
-        <v>9.95</v>
+        <v>11.93</v>
       </c>
       <c r="E37" s="1">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="F37" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="G37" s="1">
-        <v>9.95</v>
+        <v>11.93</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -1733,19 +1775,19 @@
         <v>87</v>
       </c>
       <c r="C38" s="1">
-        <v>9.99</v>
+        <v>12.84</v>
       </c>
       <c r="D38" s="1">
-        <v>9.95</v>
+        <v>12.71</v>
       </c>
       <c r="E38" s="1">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="F38" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="G38" s="1">
-        <v>9.95</v>
+        <v>12.71</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
@@ -1768,7 +1810,7 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
@@ -1794,7 +1836,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
@@ -1820,7 +1862,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1846,7 +1888,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1872,7 +1914,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1898,7 +1940,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1924,7 +1966,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -1950,7 +1992,7 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
@@ -1976,7 +2018,7 @@
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G47" s="1">
         <v>9.95</v>
@@ -2002,7 +2044,7 @@
         <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G48" s="1">
         <v>9.95</v>
@@ -2028,7 +2070,7 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
@@ -2054,7 +2096,7 @@
         <v>0.04</v>
       </c>
       <c r="F50" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G50" s="1">
         <v>9.95</v>
@@ -2080,7 +2122,7 @@
         <v>0.04</v>
       </c>
       <c r="F51" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G51" s="1">
         <v>9.95</v>
@@ -2106,12 +2148,194 @@
         <v>0.04</v>
       </c>
       <c r="F52" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G52" s="1">
         <v>9.95</v>
       </c>
       <c r="H52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D53" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F53" t="s">
+        <v>77</v>
+      </c>
+      <c r="G53" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D54" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F54" t="s">
+        <v>77</v>
+      </c>
+      <c r="G54" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" t="s">
+        <v>121</v>
+      </c>
+      <c r="C55" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D55" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F55" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D56" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F56" t="s">
+        <v>77</v>
+      </c>
+      <c r="G56" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D57" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F57" t="s">
+        <v>77</v>
+      </c>
+      <c r="G57" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D58" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F58" t="s">
+        <v>77</v>
+      </c>
+      <c r="G58" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D59" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F59" t="s">
+        <v>77</v>
+      </c>
+      <c r="G59" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H59" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-04-12.xlsx
+++ b/rapporten/prijsrapport-2026-04-12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="150">
   <si>
     <t>Product</t>
   </si>
@@ -49,232 +49,292 @@
     <t>FBR</t>
   </si>
   <si>
+    <t>SENTIO FEESTDAGEN PINK - Holly Jolly Magic - Eau de Parfum 50ml</t>
+  </si>
+  <si>
+    <t>8721055492719</t>
+  </si>
+  <si>
+    <t>Koopjesfun.nl</t>
+  </si>
+  <si>
+    <t>Bubble Bliss Fantastic Flamingo - Parfum Set Van 6 Stuks - Eau de Parfum Voor Kinderen - 6x15ml</t>
+  </si>
+  <si>
+    <t>8721055493914</t>
+  </si>
+  <si>
+    <t>Real Time - Smart Lady For Women - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658360995</t>
+  </si>
+  <si>
+    <t>Vibezz-Infusion Noir-Eau de Parfum For Her-100ml</t>
+  </si>
+  <si>
+    <t>7640158819203</t>
+  </si>
+  <si>
+    <t>Real Time Loveliness La Passione - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658360759</t>
+  </si>
+  <si>
+    <t>Omerta - Couture Cat - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658997733</t>
+  </si>
+  <si>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
+    <t>5414666014427</t>
+  </si>
+  <si>
+    <t>Juwelium</t>
+  </si>
+  <si>
+    <t>Omerta Oh My Dear L'extase parfum - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658380245</t>
+  </si>
+  <si>
+    <t>Hello Kitty Delicate Flower Eau de Parfum voor Kinderen 50ml</t>
+  </si>
+  <si>
+    <t>7640158816875</t>
+  </si>
+  <si>
+    <t>Creation Lamis Fatal Snake Magical Giftset</t>
+  </si>
+  <si>
+    <t>6291012871731</t>
+  </si>
+  <si>
+    <t>Vibezz Il Capitano - Eau de Toilette voor heren - 100ml</t>
+  </si>
+  <si>
+    <t>7640158819241</t>
+  </si>
+  <si>
+    <t>Real Time - Blue Touch - Eau De Toilette - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658350446</t>
+  </si>
+  <si>
+    <t>Real Time - Black Warrior - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658009566</t>
+  </si>
+  <si>
+    <t>Real Time - Please Call Me - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658360971</t>
+  </si>
+  <si>
+    <t>Creation Lamis Paraverse 100ml Eau de Parfum for women</t>
+  </si>
+  <si>
+    <t>6291012005082</t>
+  </si>
+  <si>
+    <t>Hello Kitty Club Eau de Parfum voor Kinderen 50 ml - I'm the rainbow after the storm</t>
+  </si>
+  <si>
+    <t>8721055493358</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493860</t>
+  </si>
+  <si>
+    <t>Minimarkt W&amp;M</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494225</t>
+  </si>
+  <si>
+    <t>Real Time Love You Red 100 ml - Eau de Parfum - Damesparfum</t>
+  </si>
+  <si>
+    <t>8715658360056</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494263</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816691</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816677</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816653</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494270</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494232</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Sparkle- Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493891</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816714</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816615</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493211</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816790</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816639</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493884</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816837</t>
+  </si>
+  <si>
+    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816813</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Smile - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493853</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Shine - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493877</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493198</t>
+  </si>
+  <si>
+    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493228</t>
+  </si>
+  <si>
+    <t>Hello Kitty - Giftset - Kisses - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>8721055493440</t>
+  </si>
+  <si>
+    <t>Vibezz-French Marine-Eau de Toilette For Him-100ml</t>
+  </si>
+  <si>
+    <t>7640158819234</t>
+  </si>
+  <si>
+    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658370505</t>
+  </si>
+  <si>
+    <t>Bliksma Retail B.V.</t>
+  </si>
+  <si>
+    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
+  </si>
+  <si>
+    <t>8715658370062</t>
+  </si>
+  <si>
+    <t>Real Time Mise Eau de Toilette100ml</t>
+  </si>
+  <si>
+    <t>8715658009733</t>
+  </si>
+  <si>
     <t>Omerta - Red Class Elixir de Luxe - Eau De Parfum - 100ML</t>
   </si>
   <si>
     <t>8715658370574</t>
   </si>
   <si>
-    <t>Koopjesfun.nl</t>
-  </si>
-  <si>
-    <t>Bubble Bliss Flamingo Giftbook Parfum Pink &amp; Proud EDP voor meisjes 50ml</t>
-  </si>
-  <si>
-    <t>8721055492184</t>
-  </si>
-  <si>
     <t>Creation Lamis Golden Wave for Men Giftset</t>
   </si>
   <si>
     <t>6291012002661</t>
   </si>
   <si>
-    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
-  </si>
-  <si>
-    <t>5414666014427</t>
-  </si>
-  <si>
-    <t>Juwelium</t>
-  </si>
-  <si>
-    <t>Real Time - Please Call Me - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658360971</t>
-  </si>
-  <si>
-    <t>Real Time Love You Red 100 ml - Eau de Parfum - Damesparfum</t>
-  </si>
-  <si>
-    <t>8715658360056</t>
-  </si>
-  <si>
-    <t>Real Time Hunted For Men - eau de toilette voor heren - 100ML</t>
-  </si>
-  <si>
-    <t>8715658350521</t>
-  </si>
-  <si>
-    <t>NG -Next Fragranse For Her- 100ml Eau de Parfum-50ml Showergel-50ml Bodylotion</t>
-  </si>
-  <si>
-    <t>8719214755829</t>
-  </si>
-  <si>
-    <t>SENTIO FEESTDAGEN PINK - Family Magical - Eau de Parfum 50ml</t>
-  </si>
-  <si>
-    <t>8721055492740</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493860</t>
-  </si>
-  <si>
-    <t>Minimarkt W&amp;M</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494225</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494263</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816691</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816677</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816653</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494270</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494232</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Sparkle- Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493891</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816714</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816615</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8721055493211</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816790</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816639</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493884</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816837</t>
-  </si>
-  <si>
-    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816813</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Smile - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493853</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Shine - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493877</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8721055493198</t>
-  </si>
-  <si>
-    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8721055493228</t>
-  </si>
-  <si>
-    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370505</t>
-  </si>
-  <si>
-    <t>Bliksma Retail B.V.</t>
-  </si>
-  <si>
-    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>8715658370062</t>
-  </si>
-  <si>
-    <t>SENTIO FEESTDAGEN PINK - Holly Jolly Magic - Eau de Parfum 50ml</t>
-  </si>
-  <si>
-    <t>8721055492719</t>
-  </si>
-  <si>
-    <t>Sentio Happy Birthday Giftset - Luxe parfum en showergel voor iedereen</t>
-  </si>
-  <si>
-    <t>8721055494140</t>
-  </si>
-  <si>
-    <t>Hello Kitty - Giftset - Kisses - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>8721055493440</t>
-  </si>
-  <si>
-    <t>Real Time - Out Of Order - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658350033</t>
+    <t>SENTIO FEESTDAGEN PINK - Happy Holidays - Body Mist 250ml</t>
+  </si>
+  <si>
+    <t>8721055493082</t>
   </si>
   <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
@@ -792,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -865,19 +925,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>13.15</v>
+        <v>12.83</v>
       </c>
       <c r="D3" s="1">
-        <v>12.38</v>
+        <v>12.13</v>
       </c>
       <c r="E3" s="1">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>12.38</v>
+        <v>12.13</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -891,19 +951,19 @@
         <v>16</v>
       </c>
       <c r="C4" s="1">
-        <v>12.95</v>
+        <v>18.25</v>
       </c>
       <c r="D4" s="1">
-        <v>12.24</v>
+        <v>17.58</v>
       </c>
       <c r="E4" s="1">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>12.24</v>
+        <v>17.58</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -917,19 +977,19 @@
         <v>18</v>
       </c>
       <c r="C5" s="1">
-        <v>12.14</v>
+        <v>13.99</v>
       </c>
       <c r="D5" s="1">
-        <v>11.62</v>
+        <v>13.35</v>
       </c>
       <c r="E5" s="1">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>11.62</v>
+        <v>13.35</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -943,19 +1003,19 @@
         <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>9.95</v>
+        <v>13.75</v>
       </c>
       <c r="D6" s="1">
-        <v>9.48</v>
+        <v>13.16</v>
       </c>
       <c r="E6" s="1">
-        <v>0.47</v>
+        <v>0.59</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>9.48</v>
+        <v>13.16</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -963,25 +1023,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
       <c r="C7" s="1">
-        <v>13.95</v>
+        <v>12.69</v>
       </c>
       <c r="D7" s="1">
-        <v>13.56</v>
+        <v>12.14</v>
       </c>
       <c r="E7" s="1">
-        <v>0.39</v>
+        <v>0.55</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>13.56</v>
+        <v>12.14</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -989,25 +1049,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
       <c r="C8" s="1">
-        <v>12.45</v>
+        <v>12.69</v>
       </c>
       <c r="D8" s="1">
-        <v>12.07</v>
+        <v>12.14</v>
       </c>
       <c r="E8" s="1">
-        <v>0.38</v>
+        <v>0.55</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>12.07</v>
+        <v>12.14</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -1015,25 +1075,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9.48</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="F9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="1">
-        <v>11.87</v>
-      </c>
-      <c r="D9" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
       <c r="G9" s="1">
-        <v>11.5</v>
+        <v>9.48</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -1047,19 +1107,19 @@
         <v>29</v>
       </c>
       <c r="C10" s="1">
-        <v>13.45</v>
+        <v>11.95</v>
       </c>
       <c r="D10" s="1">
-        <v>13.09</v>
+        <v>11.5</v>
       </c>
       <c r="E10" s="1">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="1">
-        <v>13.09</v>
+        <v>11.5</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -1073,19 +1133,19 @@
         <v>31</v>
       </c>
       <c r="C11" s="1">
-        <v>14.95</v>
+        <v>12.55</v>
       </c>
       <c r="D11" s="1">
-        <v>14.6</v>
+        <v>12.12</v>
       </c>
       <c r="E11" s="1">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1">
-        <v>14.6</v>
+        <v>12.12</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
@@ -1099,19 +1159,19 @@
         <v>33</v>
       </c>
       <c r="C12" s="1">
-        <v>5.25</v>
+        <v>13.09</v>
       </c>
       <c r="D12" s="1">
-        <v>4.99</v>
+        <v>12.68</v>
       </c>
       <c r="E12" s="1">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1">
-        <v>4.99</v>
+        <v>12.68</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -1119,25 +1179,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" s="1">
-        <v>5.25</v>
+        <v>13.75</v>
       </c>
       <c r="D13" s="1">
-        <v>4.99</v>
+        <v>13.35</v>
       </c>
       <c r="E13" s="1">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1">
-        <v>4.99</v>
+        <v>13.35</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -1145,25 +1205,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
       <c r="C14" s="1">
-        <v>5.25</v>
+        <v>13.95</v>
       </c>
       <c r="D14" s="1">
-        <v>4.99</v>
+        <v>13.56</v>
       </c>
       <c r="E14" s="1">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
-        <v>4.99</v>
+        <v>13.56</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1171,25 +1231,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
       <c r="C15" s="1">
-        <v>5.25</v>
+        <v>11.82</v>
       </c>
       <c r="D15" s="1">
-        <v>4.99</v>
+        <v>11.5</v>
       </c>
       <c r="E15" s="1">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G15" s="1">
-        <v>4.99</v>
+        <v>11.5</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
@@ -1197,25 +1257,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
       <c r="C16" s="1">
-        <v>5.25</v>
+        <v>13.16</v>
       </c>
       <c r="D16" s="1">
-        <v>4.99</v>
+        <v>12.84</v>
       </c>
       <c r="E16" s="1">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1">
-        <v>4.99</v>
+        <v>12.84</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1223,25 +1283,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
       <c r="C17" s="1">
-        <v>5.25</v>
+        <v>14.79</v>
       </c>
       <c r="D17" s="1">
-        <v>4.99</v>
+        <v>14.48</v>
       </c>
       <c r="E17" s="1">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="F17" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G17" s="1">
-        <v>4.99</v>
+        <v>14.48</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1249,25 +1309,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
         <v>45</v>
       </c>
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
       <c r="C18" s="1">
-        <v>5.25</v>
+        <v>12.15</v>
       </c>
       <c r="D18" s="1">
-        <v>4.99</v>
+        <v>11.84</v>
       </c>
       <c r="E18" s="1">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
-        <v>4.99</v>
+        <v>11.84</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
@@ -1275,10 +1335,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
         <v>47</v>
-      </c>
-      <c r="B19" t="s">
-        <v>48</v>
       </c>
       <c r="C19" s="1">
         <v>5.25</v>
@@ -1290,7 +1350,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1316,7 +1376,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1333,19 +1393,19 @@
         <v>52</v>
       </c>
       <c r="C21" s="1">
-        <v>5.25</v>
+        <v>12.07</v>
       </c>
       <c r="D21" s="1">
-        <v>4.99</v>
+        <v>11.81</v>
       </c>
       <c r="E21" s="1">
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G21" s="1">
-        <v>4.99</v>
+        <v>11.81</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -1368,7 +1428,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1394,7 +1454,7 @@
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
@@ -1420,7 +1480,7 @@
         <v>0.26</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G24" s="1">
         <v>4.99</v>
@@ -1446,7 +1506,7 @@
         <v>0.26</v>
       </c>
       <c r="F25" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G25" s="1">
         <v>4.99</v>
@@ -1472,7 +1532,7 @@
         <v>0.26</v>
       </c>
       <c r="F26" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G26" s="1">
         <v>4.99</v>
@@ -1498,7 +1558,7 @@
         <v>0.26</v>
       </c>
       <c r="F27" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G27" s="1">
         <v>4.99</v>
@@ -1524,7 +1584,7 @@
         <v>0.26</v>
       </c>
       <c r="F28" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G28" s="1">
         <v>4.99</v>
@@ -1550,7 +1610,7 @@
         <v>0.26</v>
       </c>
       <c r="F29" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G29" s="1">
         <v>4.99</v>
@@ -1576,7 +1636,7 @@
         <v>0.26</v>
       </c>
       <c r="F30" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G30" s="1">
         <v>4.99</v>
@@ -1602,7 +1662,7 @@
         <v>0.26</v>
       </c>
       <c r="F31" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G31" s="1">
         <v>4.99</v>
@@ -1628,7 +1688,7 @@
         <v>0.26</v>
       </c>
       <c r="F32" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G32" s="1">
         <v>4.99</v>
@@ -1645,19 +1705,19 @@
         <v>76</v>
       </c>
       <c r="C33" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D33" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E33" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F33" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G33" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -1665,25 +1725,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" t="s">
         <v>78</v>
       </c>
-      <c r="B34" t="s">
-        <v>79</v>
-      </c>
       <c r="C34" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D34" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E34" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G34" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -1691,25 +1751,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" t="s">
         <v>80</v>
       </c>
-      <c r="B35" t="s">
-        <v>81</v>
-      </c>
       <c r="C35" s="1">
-        <v>13.99</v>
+        <v>5.25</v>
       </c>
       <c r="D35" s="1">
-        <v>13.76</v>
+        <v>4.99</v>
       </c>
       <c r="E35" s="1">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="G35" s="1">
-        <v>13.76</v>
+        <v>4.99</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -1717,25 +1777,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" t="s">
         <v>82</v>
       </c>
-      <c r="B36" t="s">
-        <v>83</v>
-      </c>
       <c r="C36" s="1">
-        <v>14.99</v>
+        <v>5.25</v>
       </c>
       <c r="D36" s="1">
-        <v>14.78</v>
+        <v>4.99</v>
       </c>
       <c r="E36" s="1">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="G36" s="1">
-        <v>14.78</v>
+        <v>4.99</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -1743,25 +1803,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" t="s">
         <v>84</v>
       </c>
-      <c r="B37" t="s">
-        <v>85</v>
-      </c>
       <c r="C37" s="1">
-        <v>12.09</v>
+        <v>5.25</v>
       </c>
       <c r="D37" s="1">
-        <v>11.93</v>
+        <v>4.99</v>
       </c>
       <c r="E37" s="1">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="G37" s="1">
-        <v>11.93</v>
+        <v>4.99</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -1769,25 +1829,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" t="s">
         <v>86</v>
       </c>
-      <c r="B38" t="s">
-        <v>87</v>
-      </c>
       <c r="C38" s="1">
-        <v>12.84</v>
+        <v>5.25</v>
       </c>
       <c r="D38" s="1">
-        <v>12.71</v>
+        <v>4.99</v>
       </c>
       <c r="E38" s="1">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="G38" s="1">
-        <v>12.71</v>
+        <v>4.99</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
@@ -1795,25 +1855,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" t="s">
         <v>88</v>
       </c>
-      <c r="B39" t="s">
-        <v>89</v>
-      </c>
       <c r="C39" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D39" s="1">
-        <v>9.95</v>
+        <v>4.99</v>
       </c>
       <c r="E39" s="1">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="F39" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G39" s="1">
-        <v>9.95</v>
+        <v>4.99</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
@@ -1821,25 +1881,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" t="s">
         <v>90</v>
       </c>
-      <c r="B40" t="s">
-        <v>91</v>
-      </c>
       <c r="C40" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D40" s="1">
-        <v>9.95</v>
+        <v>4.99</v>
       </c>
       <c r="E40" s="1">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="F40" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G40" s="1">
-        <v>9.95</v>
+        <v>4.99</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
@@ -1847,25 +1907,25 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
         <v>92</v>
       </c>
-      <c r="B41" t="s">
-        <v>93</v>
-      </c>
       <c r="C41" s="1">
-        <v>9.99</v>
+        <v>11.93</v>
       </c>
       <c r="D41" s="1">
-        <v>9.95</v>
+        <v>11.68</v>
       </c>
       <c r="E41" s="1">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="F41" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="G41" s="1">
-        <v>9.95</v>
+        <v>11.68</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
@@ -1873,25 +1933,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" t="s">
         <v>94</v>
       </c>
-      <c r="B42" t="s">
-        <v>95</v>
-      </c>
       <c r="C42" s="1">
-        <v>9.99</v>
+        <v>12.95</v>
       </c>
       <c r="D42" s="1">
-        <v>9.95</v>
+        <v>12.71</v>
       </c>
       <c r="E42" s="1">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="F42" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="G42" s="1">
-        <v>9.95</v>
+        <v>12.71</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
@@ -1899,25 +1959,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" t="s">
         <v>96</v>
-      </c>
-      <c r="B43" t="s">
-        <v>97</v>
       </c>
       <c r="C43" s="1">
         <v>9.99</v>
       </c>
       <c r="D43" s="1">
-        <v>9.95</v>
+        <v>9.75</v>
       </c>
       <c r="E43" s="1">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="F43" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G43" s="1">
-        <v>9.95</v>
+        <v>9.75</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
@@ -1934,16 +1994,16 @@
         <v>9.99</v>
       </c>
       <c r="D44" s="1">
-        <v>9.95</v>
+        <v>9.75</v>
       </c>
       <c r="E44" s="1">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="F44" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G44" s="1">
-        <v>9.95</v>
+        <v>9.75</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
@@ -1957,19 +2017,19 @@
         <v>101</v>
       </c>
       <c r="C45" s="1">
-        <v>9.99</v>
+        <v>12.2</v>
       </c>
       <c r="D45" s="1">
-        <v>9.95</v>
+        <v>12.01</v>
       </c>
       <c r="E45" s="1">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="F45" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="G45" s="1">
-        <v>9.95</v>
+        <v>12.01</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -1983,19 +2043,19 @@
         <v>103</v>
       </c>
       <c r="C46" s="1">
-        <v>9.99</v>
+        <v>12.21</v>
       </c>
       <c r="D46" s="1">
-        <v>9.95</v>
+        <v>12.08</v>
       </c>
       <c r="E46" s="1">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="F46" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="G46" s="1">
-        <v>9.95</v>
+        <v>12.08</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2009,19 +2069,19 @@
         <v>105</v>
       </c>
       <c r="C47" s="1">
-        <v>9.99</v>
+        <v>11.62</v>
       </c>
       <c r="D47" s="1">
-        <v>9.95</v>
+        <v>11.5</v>
       </c>
       <c r="E47" s="1">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F47" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="G47" s="1">
-        <v>9.95</v>
+        <v>11.5</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -2035,19 +2095,19 @@
         <v>107</v>
       </c>
       <c r="C48" s="1">
-        <v>9.99</v>
+        <v>13.95</v>
       </c>
       <c r="D48" s="1">
-        <v>9.95</v>
+        <v>13.87</v>
       </c>
       <c r="E48" s="1">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="F48" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="G48" s="1">
-        <v>9.95</v>
+        <v>13.87</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -2070,7 +2130,7 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
@@ -2096,7 +2156,7 @@
         <v>0.04</v>
       </c>
       <c r="F50" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G50" s="1">
         <v>9.95</v>
@@ -2122,7 +2182,7 @@
         <v>0.04</v>
       </c>
       <c r="F51" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G51" s="1">
         <v>9.95</v>
@@ -2148,7 +2208,7 @@
         <v>0.04</v>
       </c>
       <c r="F52" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G52" s="1">
         <v>9.95</v>
@@ -2174,7 +2234,7 @@
         <v>0.04</v>
       </c>
       <c r="F53" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G53" s="1">
         <v>9.95</v>
@@ -2200,7 +2260,7 @@
         <v>0.04</v>
       </c>
       <c r="F54" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G54" s="1">
         <v>9.95</v>
@@ -2226,7 +2286,7 @@
         <v>0.04</v>
       </c>
       <c r="F55" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G55" s="1">
         <v>9.95</v>
@@ -2252,7 +2312,7 @@
         <v>0.04</v>
       </c>
       <c r="F56" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G56" s="1">
         <v>9.95</v>
@@ -2278,7 +2338,7 @@
         <v>0.04</v>
       </c>
       <c r="F57" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G57" s="1">
         <v>9.95</v>
@@ -2304,7 +2364,7 @@
         <v>0.04</v>
       </c>
       <c r="F58" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G58" s="1">
         <v>9.95</v>
@@ -2330,12 +2390,272 @@
         <v>0.04</v>
       </c>
       <c r="F59" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G59" s="1">
         <v>9.95</v>
       </c>
       <c r="H59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D60" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F60" t="s">
+        <v>97</v>
+      </c>
+      <c r="G60" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B61" t="s">
+        <v>133</v>
+      </c>
+      <c r="C61" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D61" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G61" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" t="s">
+        <v>135</v>
+      </c>
+      <c r="C62" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D62" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F62" t="s">
+        <v>97</v>
+      </c>
+      <c r="G62" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" t="s">
+        <v>137</v>
+      </c>
+      <c r="C63" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D63" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F63" t="s">
+        <v>97</v>
+      </c>
+      <c r="G63" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D64" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F64" t="s">
+        <v>97</v>
+      </c>
+      <c r="G64" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D65" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F65" t="s">
+        <v>97</v>
+      </c>
+      <c r="G65" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" t="s">
+        <v>143</v>
+      </c>
+      <c r="C66" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D66" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F66" t="s">
+        <v>97</v>
+      </c>
+      <c r="G66" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D67" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F67" t="s">
+        <v>97</v>
+      </c>
+      <c r="G67" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>146</v>
+      </c>
+      <c r="B68" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D68" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F68" t="s">
+        <v>97</v>
+      </c>
+      <c r="G68" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>148</v>
+      </c>
+      <c r="B69" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D69" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F69" t="s">
+        <v>97</v>
+      </c>
+      <c r="G69" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H69" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-04-12.xlsx
+++ b/rapporten/prijsrapport-2026-04-12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="124">
   <si>
     <t>Product</t>
   </si>
@@ -49,43 +49,25 @@
     <t>FBR</t>
   </si>
   <si>
-    <t>SENTIO FEESTDAGEN PINK - Holly Jolly Magic - Eau de Parfum 50ml</t>
-  </si>
-  <si>
-    <t>8721055492719</t>
+    <t>Vibezz Astrolux parfum - Eau de parfum voor haar - 100ml</t>
+  </si>
+  <si>
+    <t>7640158819173</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
   </si>
   <si>
-    <t>Bubble Bliss Fantastic Flamingo - Parfum Set Van 6 Stuks - Eau de Parfum Voor Kinderen - 6x15ml</t>
-  </si>
-  <si>
-    <t>8721055493914</t>
-  </si>
-  <si>
-    <t>Real Time - Smart Lady For Women - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658360995</t>
-  </si>
-  <si>
-    <t>Vibezz-Infusion Noir-Eau de Parfum For Her-100ml</t>
-  </si>
-  <si>
-    <t>7640158819203</t>
-  </si>
-  <si>
-    <t>Real Time Loveliness La Passione - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658360759</t>
-  </si>
-  <si>
-    <t>Omerta - Couture Cat - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658997733</t>
+    <t>Creation Lamis - Golden Wave - Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>5414666011471</t>
+  </si>
+  <si>
+    <t>Creation Lamis Paraverse 100ml Eau de Parfum for women</t>
+  </si>
+  <si>
+    <t>6291012005082</t>
   </si>
   <si>
     <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
@@ -97,58 +79,16 @@
     <t>Juwelium</t>
   </si>
   <si>
-    <t>Omerta Oh My Dear L'extase parfum - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658380245</t>
-  </si>
-  <si>
-    <t>Hello Kitty Delicate Flower Eau de Parfum voor Kinderen 50ml</t>
-  </si>
-  <si>
-    <t>7640158816875</t>
-  </si>
-  <si>
-    <t>Creation Lamis Fatal Snake Magical Giftset</t>
-  </si>
-  <si>
-    <t>6291012871731</t>
-  </si>
-  <si>
-    <t>Vibezz Il Capitano - Eau de Toilette voor heren - 100ml</t>
-  </si>
-  <si>
-    <t>7640158819241</t>
-  </si>
-  <si>
-    <t>Real Time - Blue Touch - Eau De Toilette - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658350446</t>
-  </si>
-  <si>
-    <t>Real Time - Black Warrior - Eau De Parfum - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658009566</t>
-  </si>
-  <si>
-    <t>Real Time - Please Call Me - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658360971</t>
-  </si>
-  <si>
-    <t>Creation Lamis Paraverse 100ml Eau de Parfum for women</t>
-  </si>
-  <si>
-    <t>6291012005082</t>
-  </si>
-  <si>
-    <t>Hello Kitty Club Eau de Parfum voor Kinderen 50 ml - I'm the rainbow after the storm</t>
-  </si>
-  <si>
-    <t>8721055493358</t>
+    <t>Omerta - Candy Puff - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658380801</t>
+  </si>
+  <si>
+    <t>Bubble Bliss Parfum Giftbag Glimmering Grace EDP voor meisjes 50ml</t>
+  </si>
+  <si>
+    <t>8721055494324</t>
   </si>
   <si>
     <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
@@ -166,12 +106,6 @@
     <t>8721055494225</t>
   </si>
   <si>
-    <t>Real Time Love You Red 100 ml - Eau de Parfum - Damesparfum</t>
-  </si>
-  <si>
-    <t>8715658360056</t>
-  </si>
-  <si>
     <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
   </si>
   <si>
@@ -286,16 +220,10 @@
     <t>8721055493228</t>
   </si>
   <si>
-    <t>Hello Kitty - Giftset - Kisses - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>8721055493440</t>
-  </si>
-  <si>
-    <t>Vibezz-French Marine-Eau de Toilette For Him-100ml</t>
-  </si>
-  <si>
-    <t>7640158819234</t>
+    <t>Sentio I Love You Giftset</t>
+  </si>
+  <si>
+    <t>8721055494126</t>
   </si>
   <si>
     <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
@@ -307,34 +235,28 @@
     <t>Bliksma Retail B.V.</t>
   </si>
   <si>
+    <t>Vibezz-Solitude-Eau de Toilette For Him-100ml</t>
+  </si>
+  <si>
+    <t>7640158819258</t>
+  </si>
+  <si>
     <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
   </si>
   <si>
     <t>8715658370062</t>
   </si>
   <si>
-    <t>Real Time Mise Eau de Toilette100ml</t>
-  </si>
-  <si>
-    <t>8715658009733</t>
-  </si>
-  <si>
-    <t>Omerta - Red Class Elixir de Luxe - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370574</t>
-  </si>
-  <si>
-    <t>Creation Lamis Golden Wave for Men Giftset</t>
-  </si>
-  <si>
-    <t>6291012002661</t>
-  </si>
-  <si>
-    <t>SENTIO FEESTDAGEN PINK - Happy Holidays - Body Mist 250ml</t>
-  </si>
-  <si>
-    <t>8721055493082</t>
+    <t>Omerta - Vanilla Fun - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658999447</t>
+  </si>
+  <si>
+    <t>Creation Lamis Catsuit Woman Eau de Parfum For Women 100 ml</t>
+  </si>
+  <si>
+    <t>6151010029070</t>
   </si>
   <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
@@ -852,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -899,13 +821,13 @@
         <v>9</v>
       </c>
       <c r="C2" s="1">
-        <v>14.99</v>
+        <v>13.63</v>
       </c>
       <c r="D2" s="1">
         <v>12.49</v>
       </c>
       <c r="E2" s="1">
-        <v>2.5</v>
+        <v>1.14</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -925,19 +847,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>12.83</v>
+        <v>12.71</v>
       </c>
       <c r="D3" s="1">
-        <v>12.13</v>
+        <v>12.02</v>
       </c>
       <c r="E3" s="1">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>12.13</v>
+        <v>12.02</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -951,19 +873,19 @@
         <v>16</v>
       </c>
       <c r="C4" s="1">
-        <v>18.25</v>
+        <v>12.99</v>
       </c>
       <c r="D4" s="1">
-        <v>17.58</v>
+        <v>12.35</v>
       </c>
       <c r="E4" s="1">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>17.58</v>
+        <v>12.35</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -977,19 +899,19 @@
         <v>18</v>
       </c>
       <c r="C5" s="1">
-        <v>13.99</v>
+        <v>14.48</v>
       </c>
       <c r="D5" s="1">
-        <v>13.35</v>
+        <v>13.91</v>
       </c>
       <c r="E5" s="1">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>13.35</v>
+        <v>13.91</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -1003,19 +925,19 @@
         <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>13.75</v>
+        <v>9.95</v>
       </c>
       <c r="D6" s="1">
-        <v>13.16</v>
+        <v>9.48</v>
       </c>
       <c r="E6" s="1">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1">
-        <v>13.16</v>
+        <v>9.48</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -1023,25 +945,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
-        <v>12.69</v>
+        <v>12.95</v>
       </c>
       <c r="D7" s="1">
-        <v>12.14</v>
+        <v>12.59</v>
       </c>
       <c r="E7" s="1">
-        <v>0.55</v>
+        <v>0.36</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>12.14</v>
+        <v>12.59</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -1049,25 +971,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1">
-        <v>12.69</v>
+        <v>12.95</v>
       </c>
       <c r="D8" s="1">
-        <v>12.14</v>
+        <v>12.62</v>
       </c>
       <c r="E8" s="1">
-        <v>0.55</v>
+        <v>0.33</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>12.14</v>
+        <v>12.62</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -1075,25 +997,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1">
-        <v>9.95</v>
+        <v>5.25</v>
       </c>
       <c r="D9" s="1">
-        <v>9.48</v>
+        <v>4.99</v>
       </c>
       <c r="E9" s="1">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1">
-        <v>9.48</v>
+        <v>4.99</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -1101,25 +1023,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1">
-        <v>11.95</v>
-      </c>
-      <c r="D10" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
       <c r="G10" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -1127,25 +1049,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1">
-        <v>12.55</v>
+        <v>5.25</v>
       </c>
       <c r="D11" s="1">
-        <v>12.12</v>
+        <v>4.99</v>
       </c>
       <c r="E11" s="1">
-        <v>0.43</v>
+        <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1">
-        <v>12.12</v>
+        <v>4.99</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
@@ -1153,25 +1075,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1">
-        <v>13.09</v>
+        <v>5.25</v>
       </c>
       <c r="D12" s="1">
-        <v>12.68</v>
+        <v>4.99</v>
       </c>
       <c r="E12" s="1">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G12" s="1">
-        <v>12.68</v>
+        <v>4.99</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -1179,25 +1101,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1">
-        <v>13.75</v>
+        <v>5.25</v>
       </c>
       <c r="D13" s="1">
-        <v>13.35</v>
+        <v>4.99</v>
       </c>
       <c r="E13" s="1">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G13" s="1">
-        <v>13.35</v>
+        <v>4.99</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -1205,25 +1127,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1">
-        <v>13.95</v>
+        <v>5.25</v>
       </c>
       <c r="D14" s="1">
-        <v>13.56</v>
+        <v>4.99</v>
       </c>
       <c r="E14" s="1">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G14" s="1">
-        <v>13.56</v>
+        <v>4.99</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1231,25 +1153,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1">
-        <v>11.82</v>
+        <v>5.25</v>
       </c>
       <c r="D15" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="E15" s="1">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G15" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
@@ -1257,25 +1179,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1">
-        <v>13.16</v>
+        <v>5.25</v>
       </c>
       <c r="D16" s="1">
-        <v>12.84</v>
+        <v>4.99</v>
       </c>
       <c r="E16" s="1">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G16" s="1">
-        <v>12.84</v>
+        <v>4.99</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1283,25 +1205,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1">
-        <v>14.79</v>
+        <v>5.25</v>
       </c>
       <c r="D17" s="1">
-        <v>14.48</v>
+        <v>4.99</v>
       </c>
       <c r="E17" s="1">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G17" s="1">
-        <v>14.48</v>
+        <v>4.99</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1309,25 +1231,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1">
-        <v>12.15</v>
+        <v>5.25</v>
       </c>
       <c r="D18" s="1">
-        <v>11.84</v>
+        <v>4.99</v>
       </c>
       <c r="E18" s="1">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G18" s="1">
-        <v>11.84</v>
+        <v>4.99</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
@@ -1335,10 +1257,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1">
         <v>5.25</v>
@@ -1350,7 +1272,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1376,7 +1298,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1393,19 +1315,19 @@
         <v>52</v>
       </c>
       <c r="C21" s="1">
-        <v>12.07</v>
+        <v>5.25</v>
       </c>
       <c r="D21" s="1">
-        <v>11.81</v>
+        <v>4.99</v>
       </c>
       <c r="E21" s="1">
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G21" s="1">
-        <v>11.81</v>
+        <v>4.99</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -1428,7 +1350,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1454,7 +1376,7 @@
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
@@ -1480,7 +1402,7 @@
         <v>0.26</v>
       </c>
       <c r="F24" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G24" s="1">
         <v>4.99</v>
@@ -1506,7 +1428,7 @@
         <v>0.26</v>
       </c>
       <c r="F25" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G25" s="1">
         <v>4.99</v>
@@ -1532,7 +1454,7 @@
         <v>0.26</v>
       </c>
       <c r="F26" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G26" s="1">
         <v>4.99</v>
@@ -1558,7 +1480,7 @@
         <v>0.26</v>
       </c>
       <c r="F27" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G27" s="1">
         <v>4.99</v>
@@ -1584,7 +1506,7 @@
         <v>0.26</v>
       </c>
       <c r="F28" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G28" s="1">
         <v>4.99</v>
@@ -1610,7 +1532,7 @@
         <v>0.26</v>
       </c>
       <c r="F29" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G29" s="1">
         <v>4.99</v>
@@ -1627,19 +1549,19 @@
         <v>70</v>
       </c>
       <c r="C30" s="1">
-        <v>5.25</v>
+        <v>12.89</v>
       </c>
       <c r="D30" s="1">
-        <v>4.99</v>
+        <v>12.64</v>
       </c>
       <c r="E30" s="1">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="G30" s="1">
-        <v>4.99</v>
+        <v>12.64</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -1653,19 +1575,19 @@
         <v>72</v>
       </c>
       <c r="C31" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D31" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E31" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="G31" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -1673,25 +1595,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" s="1">
-        <v>5.25</v>
+        <v>12.95</v>
       </c>
       <c r="D32" s="1">
-        <v>4.99</v>
+        <v>12.71</v>
       </c>
       <c r="E32" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="G32" s="1">
-        <v>4.99</v>
+        <v>12.71</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -1699,25 +1621,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D33" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E33" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F33" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="G33" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -1725,25 +1647,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" s="1">
-        <v>5.25</v>
+        <v>12.89</v>
       </c>
       <c r="D34" s="1">
-        <v>4.99</v>
+        <v>12.77</v>
       </c>
       <c r="E34" s="1">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="F34" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1">
-        <v>4.99</v>
+        <v>12.77</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -1751,25 +1673,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="1">
-        <v>5.25</v>
+        <v>12.95</v>
       </c>
       <c r="D35" s="1">
-        <v>4.99</v>
+        <v>12.9</v>
       </c>
       <c r="E35" s="1">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="F35" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="G35" s="1">
-        <v>4.99</v>
+        <v>12.9</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -1777,25 +1699,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D36" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E36" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="G36" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -1803,25 +1725,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D37" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E37" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="G37" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -1829,25 +1751,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D38" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E38" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="G38" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
@@ -1855,25 +1777,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D39" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E39" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="G39" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
@@ -1881,25 +1803,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D40" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E40" s="1">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="G40" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
@@ -1907,25 +1829,25 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1">
-        <v>11.93</v>
+        <v>9.99</v>
       </c>
       <c r="D41" s="1">
-        <v>11.68</v>
+        <v>9.95</v>
       </c>
       <c r="E41" s="1">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G41" s="1">
-        <v>11.68</v>
+        <v>9.95</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
@@ -1933,25 +1855,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" s="1">
-        <v>12.95</v>
+        <v>9.99</v>
       </c>
       <c r="D42" s="1">
-        <v>12.71</v>
+        <v>9.95</v>
       </c>
       <c r="E42" s="1">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G42" s="1">
-        <v>12.71</v>
+        <v>9.95</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
@@ -1959,25 +1881,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" s="1">
         <v>9.99</v>
       </c>
       <c r="D43" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="E43" s="1">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G43" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
@@ -1994,16 +1916,16 @@
         <v>9.99</v>
       </c>
       <c r="D44" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="E44" s="1">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G44" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
@@ -2017,19 +1939,19 @@
         <v>101</v>
       </c>
       <c r="C45" s="1">
-        <v>12.2</v>
+        <v>9.99</v>
       </c>
       <c r="D45" s="1">
-        <v>12.01</v>
+        <v>9.95</v>
       </c>
       <c r="E45" s="1">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G45" s="1">
-        <v>12.01</v>
+        <v>9.95</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -2043,19 +1965,19 @@
         <v>103</v>
       </c>
       <c r="C46" s="1">
-        <v>12.21</v>
+        <v>9.99</v>
       </c>
       <c r="D46" s="1">
-        <v>12.08</v>
+        <v>9.95</v>
       </c>
       <c r="E46" s="1">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G46" s="1">
-        <v>12.08</v>
+        <v>9.95</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2069,19 +1991,19 @@
         <v>105</v>
       </c>
       <c r="C47" s="1">
-        <v>11.62</v>
+        <v>9.99</v>
       </c>
       <c r="D47" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="E47" s="1">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G47" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -2095,19 +2017,19 @@
         <v>107</v>
       </c>
       <c r="C48" s="1">
-        <v>13.95</v>
+        <v>9.99</v>
       </c>
       <c r="D48" s="1">
-        <v>13.87</v>
+        <v>9.95</v>
       </c>
       <c r="E48" s="1">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G48" s="1">
-        <v>13.87</v>
+        <v>9.95</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -2130,7 +2052,7 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
@@ -2156,7 +2078,7 @@
         <v>0.04</v>
       </c>
       <c r="F50" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G50" s="1">
         <v>9.95</v>
@@ -2182,7 +2104,7 @@
         <v>0.04</v>
       </c>
       <c r="F51" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G51" s="1">
         <v>9.95</v>
@@ -2208,7 +2130,7 @@
         <v>0.04</v>
       </c>
       <c r="F52" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G52" s="1">
         <v>9.95</v>
@@ -2234,7 +2156,7 @@
         <v>0.04</v>
       </c>
       <c r="F53" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G53" s="1">
         <v>9.95</v>
@@ -2260,7 +2182,7 @@
         <v>0.04</v>
       </c>
       <c r="F54" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G54" s="1">
         <v>9.95</v>
@@ -2286,7 +2208,7 @@
         <v>0.04</v>
       </c>
       <c r="F55" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G55" s="1">
         <v>9.95</v>
@@ -2312,350 +2234,12 @@
         <v>0.04</v>
       </c>
       <c r="F56" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G56" s="1">
         <v>9.95</v>
       </c>
       <c r="H56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" t="s">
-        <v>125</v>
-      </c>
-      <c r="C57" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D57" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E57" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G57" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" t="s">
-        <v>127</v>
-      </c>
-      <c r="C58" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D58" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F58" t="s">
-        <v>97</v>
-      </c>
-      <c r="G58" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H58" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>128</v>
-      </c>
-      <c r="B59" t="s">
-        <v>129</v>
-      </c>
-      <c r="C59" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D59" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E59" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F59" t="s">
-        <v>97</v>
-      </c>
-      <c r="G59" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>130</v>
-      </c>
-      <c r="B60" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D60" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F60" t="s">
-        <v>97</v>
-      </c>
-      <c r="G60" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>132</v>
-      </c>
-      <c r="B61" t="s">
-        <v>133</v>
-      </c>
-      <c r="C61" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D61" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E61" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F61" t="s">
-        <v>97</v>
-      </c>
-      <c r="G61" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>134</v>
-      </c>
-      <c r="B62" t="s">
-        <v>135</v>
-      </c>
-      <c r="C62" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D62" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F62" t="s">
-        <v>97</v>
-      </c>
-      <c r="G62" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>136</v>
-      </c>
-      <c r="B63" t="s">
-        <v>137</v>
-      </c>
-      <c r="C63" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D63" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F63" t="s">
-        <v>97</v>
-      </c>
-      <c r="G63" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>138</v>
-      </c>
-      <c r="B64" t="s">
-        <v>139</v>
-      </c>
-      <c r="C64" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D64" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F64" t="s">
-        <v>97</v>
-      </c>
-      <c r="G64" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>140</v>
-      </c>
-      <c r="B65" t="s">
-        <v>141</v>
-      </c>
-      <c r="C65" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D65" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F65" t="s">
-        <v>97</v>
-      </c>
-      <c r="G65" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>143</v>
-      </c>
-      <c r="C66" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D66" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F66" t="s">
-        <v>97</v>
-      </c>
-      <c r="G66" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>144</v>
-      </c>
-      <c r="B67" t="s">
-        <v>145</v>
-      </c>
-      <c r="C67" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D67" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F67" t="s">
-        <v>97</v>
-      </c>
-      <c r="G67" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>146</v>
-      </c>
-      <c r="B68" t="s">
-        <v>147</v>
-      </c>
-      <c r="C68" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D68" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F68" t="s">
-        <v>97</v>
-      </c>
-      <c r="G68" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>148</v>
-      </c>
-      <c r="B69" t="s">
-        <v>149</v>
-      </c>
-      <c r="C69" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D69" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E69" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F69" t="s">
-        <v>97</v>
-      </c>
-      <c r="G69" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H69" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-04-12.xlsx
+++ b/rapporten/prijsrapport-2026-04-12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="122">
   <si>
     <t>Product</t>
   </si>
@@ -49,10 +49,10 @@
     <t>FBR</t>
   </si>
   <si>
-    <t>Vibezz Astrolux parfum - Eau de parfum voor haar - 100ml</t>
-  </si>
-  <si>
-    <t>7640158819173</t>
+    <t>De La Mare Parfum Raggio Di Sole 73 Vanilla &amp; Orchid Eau de Parfum 100 ml</t>
+  </si>
+  <si>
+    <t>8721055498179</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
@@ -64,10 +64,10 @@
     <t>5414666011471</t>
   </si>
   <si>
-    <t>Creation Lamis Paraverse 100ml Eau de Parfum for women</t>
-  </si>
-  <si>
-    <t>6291012005082</t>
+    <t>SENTIO FEESTDAGEN - Kerst Giftset Christmas Tree - Merry Christmas</t>
+  </si>
+  <si>
+    <t>8721055492757</t>
   </si>
   <si>
     <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
@@ -79,16 +79,16 @@
     <t>Juwelium</t>
   </si>
   <si>
-    <t>Omerta - Candy Puff - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658380801</t>
-  </si>
-  <si>
-    <t>Bubble Bliss Parfum Giftbag Glimmering Grace EDP voor meisjes 50ml</t>
-  </si>
-  <si>
-    <t>8721055494324</t>
+    <t>Omerta -Meet Me Extreme- 100ml Eau de Toilette for men</t>
+  </si>
+  <si>
+    <t>8715658370420</t>
+  </si>
+  <si>
+    <t>NG Heaven's Body Men Eau de Toilette 100ml -Voor Mannen.</t>
+  </si>
+  <si>
+    <t>8719214753344</t>
   </si>
   <si>
     <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
@@ -220,12 +220,6 @@
     <t>8721055493228</t>
   </si>
   <si>
-    <t>Sentio I Love You Giftset</t>
-  </si>
-  <si>
-    <t>8721055494126</t>
-  </si>
-  <si>
     <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
   </si>
   <si>
@@ -235,28 +229,22 @@
     <t>Bliksma Retail B.V.</t>
   </si>
   <si>
-    <t>Vibezz-Solitude-Eau de Toilette For Him-100ml</t>
-  </si>
-  <si>
-    <t>7640158819258</t>
-  </si>
-  <si>
     <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
   </si>
   <si>
     <t>8715658370062</t>
   </si>
   <si>
-    <t>Omerta - Vanilla Fun - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658999447</t>
-  </si>
-  <si>
-    <t>Creation Lamis Catsuit Woman Eau de Parfum For Women 100 ml</t>
-  </si>
-  <si>
-    <t>6151010029070</t>
+    <t>Real Time - Black Rose - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658008354</t>
+  </si>
+  <si>
+    <t>Street Looks - Pure Courage - Eau de Toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658013082</t>
   </si>
   <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
@@ -383,6 +371,12 @@
   </si>
   <si>
     <t>8715658380580</t>
+  </si>
+  <si>
+    <t>NG Lightness Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8719214758363</t>
   </si>
 </sst>
 </file>
@@ -774,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -847,19 +841,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>12.71</v>
+        <v>13.95</v>
       </c>
       <c r="D3" s="1">
-        <v>12.02</v>
+        <v>13.32</v>
       </c>
       <c r="E3" s="1">
-        <v>0.69</v>
+        <v>0.63</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>12.02</v>
+        <v>13.32</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -873,19 +867,19 @@
         <v>16</v>
       </c>
       <c r="C4" s="1">
-        <v>12.99</v>
+        <v>12.35</v>
       </c>
       <c r="D4" s="1">
-        <v>12.35</v>
+        <v>11.74</v>
       </c>
       <c r="E4" s="1">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>12.35</v>
+        <v>11.74</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -899,19 +893,19 @@
         <v>18</v>
       </c>
       <c r="C5" s="1">
-        <v>14.48</v>
+        <v>12.99</v>
       </c>
       <c r="D5" s="1">
-        <v>13.91</v>
+        <v>12.41</v>
       </c>
       <c r="E5" s="1">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>13.91</v>
+        <v>12.41</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -951,19 +945,19 @@
         <v>23</v>
       </c>
       <c r="C7" s="1">
-        <v>12.95</v>
+        <v>12.25</v>
       </c>
       <c r="D7" s="1">
-        <v>12.59</v>
+        <v>11.82</v>
       </c>
       <c r="E7" s="1">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>12.59</v>
+        <v>11.82</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -977,19 +971,19 @@
         <v>25</v>
       </c>
       <c r="C8" s="1">
-        <v>12.95</v>
+        <v>12.5</v>
       </c>
       <c r="D8" s="1">
-        <v>12.62</v>
+        <v>12.21</v>
       </c>
       <c r="E8" s="1">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>12.62</v>
+        <v>12.21</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -1549,19 +1543,19 @@
         <v>70</v>
       </c>
       <c r="C30" s="1">
-        <v>12.89</v>
+        <v>9.99</v>
       </c>
       <c r="D30" s="1">
-        <v>12.64</v>
+        <v>9.75</v>
       </c>
       <c r="E30" s="1">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="G30" s="1">
-        <v>12.64</v>
+        <v>9.75</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -1569,10 +1563,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C31" s="1">
         <v>9.99</v>
@@ -1584,7 +1578,7 @@
         <v>0.24</v>
       </c>
       <c r="F31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G31" s="1">
         <v>9.75</v>
@@ -1601,19 +1595,19 @@
         <v>75</v>
       </c>
       <c r="C32" s="1">
-        <v>12.95</v>
+        <v>11.9</v>
       </c>
       <c r="D32" s="1">
-        <v>12.71</v>
+        <v>11.76</v>
       </c>
       <c r="E32" s="1">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
       </c>
       <c r="G32" s="1">
-        <v>12.71</v>
+        <v>11.76</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -1627,19 +1621,19 @@
         <v>77</v>
       </c>
       <c r="C33" s="1">
-        <v>9.99</v>
+        <v>12.25</v>
       </c>
       <c r="D33" s="1">
-        <v>9.75</v>
+        <v>12.14</v>
       </c>
       <c r="E33" s="1">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="F33" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="G33" s="1">
-        <v>9.75</v>
+        <v>12.14</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -1653,19 +1647,19 @@
         <v>79</v>
       </c>
       <c r="C34" s="1">
-        <v>12.89</v>
+        <v>9.99</v>
       </c>
       <c r="D34" s="1">
-        <v>12.77</v>
+        <v>9.95</v>
       </c>
       <c r="E34" s="1">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="G34" s="1">
-        <v>12.77</v>
+        <v>9.95</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -1679,19 +1673,19 @@
         <v>81</v>
       </c>
       <c r="C35" s="1">
-        <v>12.95</v>
+        <v>9.99</v>
       </c>
       <c r="D35" s="1">
-        <v>12.9</v>
+        <v>9.95</v>
       </c>
       <c r="E35" s="1">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="G35" s="1">
-        <v>12.9</v>
+        <v>9.95</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -1714,7 +1708,7 @@
         <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G36" s="1">
         <v>9.95</v>
@@ -1740,7 +1734,7 @@
         <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G37" s="1">
         <v>9.95</v>
@@ -1766,7 +1760,7 @@
         <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G38" s="1">
         <v>9.95</v>
@@ -1792,7 +1786,7 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
@@ -1818,7 +1812,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
@@ -1844,7 +1838,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1870,7 +1864,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1896,7 +1890,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1922,7 +1916,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1948,7 +1942,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -1974,7 +1968,7 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
@@ -2000,7 +1994,7 @@
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G47" s="1">
         <v>9.95</v>
@@ -2026,7 +2020,7 @@
         <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G48" s="1">
         <v>9.95</v>
@@ -2052,7 +2046,7 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
@@ -2078,7 +2072,7 @@
         <v>0.04</v>
       </c>
       <c r="F50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G50" s="1">
         <v>9.95</v>
@@ -2104,7 +2098,7 @@
         <v>0.04</v>
       </c>
       <c r="F51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G51" s="1">
         <v>9.95</v>
@@ -2130,7 +2124,7 @@
         <v>0.04</v>
       </c>
       <c r="F52" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G52" s="1">
         <v>9.95</v>
@@ -2156,7 +2150,7 @@
         <v>0.04</v>
       </c>
       <c r="F53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G53" s="1">
         <v>9.95</v>
@@ -2182,7 +2176,7 @@
         <v>0.04</v>
       </c>
       <c r="F54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G54" s="1">
         <v>9.95</v>
@@ -2199,47 +2193,21 @@
         <v>121</v>
       </c>
       <c r="C55" s="1">
-        <v>9.99</v>
+        <v>11.85</v>
       </c>
       <c r="D55" s="1">
-        <v>9.95</v>
+        <v>11.82</v>
       </c>
       <c r="E55" s="1">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F55" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="G55" s="1">
-        <v>9.95</v>
+        <v>11.82</v>
       </c>
       <c r="H55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" t="s">
-        <v>123</v>
-      </c>
-      <c r="C56" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D56" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F56" t="s">
-        <v>73</v>
-      </c>
-      <c r="G56" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H56" t="s">
         <v>11</v>
       </c>
     </row>
